--- a/media/exports/reports/2025-10/job-margins.xlsx
+++ b/media/exports/reports/2025-10/job-margins.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1155,176 +1155,208 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Technician time charged, October</t>
+        </is>
+      </c>
+      <c r="B73" s="8">
+        <f>Workings!B289</f>
+        <v/>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>67.3% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Materials charged, October</t>
+        </is>
+      </c>
+      <c r="B74" s="8">
+        <f>Workings!B301</f>
+        <v/>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>$5,610 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, October 2025</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr"/>
-      <c r="B75" s="7" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (7)</t>
-        </is>
-      </c>
-      <c r="B76" s="8">
-        <f>Workings!B288</f>
-        <v/>
-      </c>
-      <c r="C76" s="11">
-        <f>Workings!B287</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (3)</t>
-        </is>
-      </c>
-      <c r="B77" s="8">
-        <f>Workings!B299</f>
-        <v/>
-      </c>
-      <c r="C77" s="11">
-        <f>Workings!B298</f>
-        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2-hour call-outs (9)</t>
+          <t>1-hour call-outs (7)</t>
         </is>
       </c>
       <c r="B78" s="8">
-        <f>Workings!B310</f>
+        <f>Workings!B314</f>
         <v/>
       </c>
       <c r="C78" s="11">
-        <f>Workings!B309</f>
+        <f>Workings!B313</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (8)</t>
+          <t>1.5-hour call-outs (3)</t>
         </is>
       </c>
       <c r="B79" s="8">
-        <f>Workings!B321</f>
+        <f>Workings!B327</f>
         <v/>
       </c>
       <c r="C79" s="11">
-        <f>Workings!B320</f>
+        <f>Workings!B326</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3-hour call-outs (10)</t>
+          <t>2-hour call-outs (9)</t>
         </is>
       </c>
       <c r="B80" s="8">
-        <f>Workings!B332</f>
+        <f>Workings!B340</f>
         <v/>
       </c>
       <c r="C80" s="11">
-        <f>Workings!B331</f>
+        <f>Workings!B339</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>2.5-hour call-outs (8)</t>
+        </is>
+      </c>
+      <c r="B81" s="8">
+        <f>Workings!B353</f>
+        <v/>
+      </c>
+      <c r="C81" s="11">
+        <f>Workings!B352</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (10)</t>
+        </is>
+      </c>
+      <c r="B82" s="8">
+        <f>Workings!B366</f>
+        <v/>
+      </c>
+      <c r="C82" s="11">
+        <f>Workings!B365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B81" s="8">
-        <f>Workings!B343</f>
-        <v/>
-      </c>
-      <c r="C81" s="11">
-        <f>Workings!B342</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="B83" s="8">
+        <f>Workings!B379</f>
+        <v/>
+      </c>
+      <c r="C83" s="11">
+        <f>Workings!B378</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="45" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>43 call-outs in October made a 43.3% job gross margin between them. Gross margins run from 37.8% to 45.9% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85"/>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>43 call-outs in October billed $15,005 of technician time and $7,293 of materials ($5,610 at cost plus 30%), and made a 43.3% job gross margin between them. Gross margins run from 37.8% to 45.9% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Call-outs: 43.3% gross margin, below the 52.5% needed to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="91"/>
-    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A89:D89"/>
     <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A86:D86"/>
     <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A87:D87"/>
     <mergeCell ref="A65:D65"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A84:D84"/>
     <mergeCell ref="A49:D49"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -1352,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C346"/>
+  <dimension ref="A1:C382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3676,14 +3708,14 @@
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>1-hour call-outs (7)</t>
+          <t>Call-out revenue, October</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="12" t="inlineStr">
         <is>
-          <t>Call-outs of this length in October, added together</t>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -3698,498 +3730,818 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B283" s="13" t="n">
-        <v>7</v>
+        <v>15005</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B284" s="13" t="n">
-        <v>2068</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B285" s="13" t="n">
-        <v>-810</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B285" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B286" s="13" t="n">
-        <v>-476</v>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B286" s="13">
+        <f>B284*(1+B285)</f>
+        <v/>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B287" s="13">
-        <f>B284+B285+B286</f>
-        <v/>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B287" s="13" t="n">
+        <v>7293</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B288" s="16">
-        <f>B287/B284</f>
-        <v/>
-      </c>
-    </row>
-    <row r="289"/>
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B288" s="13">
+        <f>B283+B287</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B289" s="16">
+        <f>B283/B288</f>
+        <v/>
+      </c>
+    </row>
     <row r="290"/>
-    <row r="291">
-      <c r="A291" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (3)</t>
-        </is>
-      </c>
-    </row>
+    <row r="291"/>
     <row r="292">
-      <c r="A292" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in October, added together</t>
+      <c r="A292" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, October</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="6" t="inlineStr"/>
-      <c r="B293" s="7" t="inlineStr">
+      <c r="A293" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="6" t="inlineStr"/>
+      <c r="B294" s="7" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B294" s="13" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B295" s="13" t="n">
-        <v>1288</v>
+        <v>15005</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B296" s="13" t="n">
-        <v>-490</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B297" s="13" t="n">
-        <v>-306</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B297" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
       <c r="B298" s="13">
-        <f>B295+B296+B297</f>
+        <f>B296*(1+B297)</f>
         <v/>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B299" s="16">
-        <f>B298/B295</f>
-        <v/>
-      </c>
-    </row>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302">
-      <c r="A302" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="12" t="inlineStr">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B299" s="13" t="n">
+        <v>7293</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B300" s="13">
+        <f>B295+B299</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B301" s="16">
+        <f>B295/B300</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in October, added together</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" s="6" t="inlineStr"/>
-      <c r="B304" s="7" t="inlineStr">
+    <row r="306">
+      <c r="A306" s="6" t="inlineStr"/>
+      <c r="B306" s="7" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B305" s="13" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B306" s="13" t="n">
-        <v>4443</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Call-outs</t>
         </is>
       </c>
       <c r="B307" s="13" t="n">
-        <v>-1410</v>
+        <v>7</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B308" s="13" t="n">
-        <v>-1224</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B309" s="13" t="n">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B310" s="13">
+        <f>B308+B309</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B311" s="13" t="n">
+        <v>-810</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B312" s="13" t="n">
+        <v>-476</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B309" s="13">
-        <f>B306+B307+B308</f>
-        <v/>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="15" t="inlineStr">
+      <c r="B313" s="13">
+        <f>B310+B311+B312</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B310" s="16">
-        <f>B309/B306</f>
-        <v/>
-      </c>
-    </row>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313">
-      <c r="A313" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="12" t="inlineStr">
+      <c r="B314" s="16">
+        <f>B313/B310</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in October, added together</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" s="6" t="inlineStr"/>
-      <c r="B315" s="7" t="inlineStr">
+    <row r="319">
+      <c r="A319" s="6" t="inlineStr"/>
+      <c r="B319" s="7" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B316" s="13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B317" s="13" t="n">
-        <v>4134</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B318" s="13" t="n">
-        <v>-950</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B319" s="13" t="n">
-        <v>-1360</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B320" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B321" s="13" t="n">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B322" s="13" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B323" s="13">
+        <f>B321+B322</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B324" s="13" t="n">
+        <v>-490</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B325" s="13" t="n">
+        <v>-306</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B320" s="13">
-        <f>B317+B318+B319</f>
-        <v/>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="15" t="inlineStr">
+      <c r="B326" s="13">
+        <f>B323+B324+B325</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B321" s="16">
-        <f>B320/B317</f>
-        <v/>
-      </c>
-    </row>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324">
-      <c r="A324" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="12" t="inlineStr">
+      <c r="B327" s="16">
+        <f>B326/B323</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330">
+      <c r="A330" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in October, added together</t>
         </is>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" s="6" t="inlineStr"/>
-      <c r="B326" s="7" t="inlineStr">
+    <row r="332">
+      <c r="A332" s="6" t="inlineStr"/>
+      <c r="B332" s="7" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
+    <row r="333">
+      <c r="A333" t="inlineStr">
         <is>
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B327" s="13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
+      <c r="B333" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B334" s="13" t="n">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B335" s="13" t="n">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B328" s="13" t="n">
-        <v>5780</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B329" s="13" t="n">
-        <v>-1100</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B330" s="13" t="n">
-        <v>-2040</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B331" s="13">
-        <f>B328+B329+B330</f>
-        <v/>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B332" s="16">
-        <f>B331/B328</f>
-        <v/>
-      </c>
-    </row>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335">
-      <c r="A335" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in October, added together</t>
-        </is>
+      <c r="B336" s="13">
+        <f>B334+B335</f>
+        <v/>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="6" t="inlineStr"/>
-      <c r="B337" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B337" s="13" t="n">
+        <v>-1410</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time at cost</t>
         </is>
       </c>
       <c r="B338" s="13" t="n">
-        <v>6</v>
+        <v>-1224</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B339" s="13">
+        <f>B336+B337+B338</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B340" s="16">
+        <f>B339/B336</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in October, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="6" t="inlineStr"/>
+      <c r="B345" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B346" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B347" s="13" t="n">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B348" s="13" t="n">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B339" s="13" t="n">
-        <v>4585</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B340" s="13" t="n">
+      <c r="B349" s="13">
+        <f>B347+B348</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B350" s="13" t="n">
+        <v>-950</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B351" s="13" t="n">
+        <v>-1360</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B352" s="13">
+        <f>B349+B350+B351</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B353" s="16">
+        <f>B352/B349</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356">
+      <c r="A356" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in October, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="6" t="inlineStr"/>
+      <c r="B358" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B359" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B360" s="13" t="n">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B361" s="13" t="n">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B362" s="13">
+        <f>B360+B361</f>
+        <v/>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B363" s="13" t="n">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B364" s="13" t="n">
+        <v>-2040</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B365" s="13">
+        <f>B362+B363+B364</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B366" s="16">
+        <f>B365/B362</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in October, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="6" t="inlineStr"/>
+      <c r="B371" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B372" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B373" s="13" t="n">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B374" s="13" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B375" s="13">
+        <f>B373+B374</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B376" s="13" t="n">
         <v>-850</v>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
+    <row r="377">
+      <c r="A377" t="inlineStr">
         <is>
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B341" s="13" t="n">
+      <c r="B377" s="13" t="n">
         <v>-1632</v>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B342" s="13">
-        <f>B339+B340+B341</f>
-        <v/>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="15" t="inlineStr">
+      <c r="B378" s="13">
+        <f>B375+B376+B377</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B343" s="16">
-        <f>B342/B339</f>
-        <v/>
-      </c>
-    </row>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
+      <c r="B379" s="16">
+        <f>B378/B375</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4202,7 +4554,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="13" manualBreakCount="13">
+  <rowBreaks count="14" manualBreakCount="14">
     <brk id="30" min="0" max="16383" man="1"/>
     <brk id="57" min="0" max="16383" man="1"/>
     <brk id="79" min="0" max="16383" man="1"/>
@@ -4214,8 +4566,9 @@
     <brk id="231" min="0" max="16383" man="1"/>
     <brk id="257" min="0" max="16383" man="1"/>
     <brk id="279" min="0" max="16383" man="1"/>
-    <brk id="301" min="0" max="16383" man="1"/>
-    <brk id="323" min="0" max="16383" man="1"/>
+    <brk id="303" min="0" max="16383" man="1"/>
+    <brk id="329" min="0" max="16383" man="1"/>
+    <brk id="355" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2025-10/job-margins.xlsx
+++ b/media/exports/reports/2025-10/job-margins.xlsx
@@ -25,48 +25,58 @@
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;[Red](#,##0.0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
@@ -99,36 +109,36 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1363,8 +1373,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4547,8 +4557,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6267,8 +6277,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2025-10/job-margins.xlsx
+++ b/media/exports/reports/2025-10/job-margins.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Before overheads, so this is not profit. Pick a type of job and every number, chart and note on the page follows it.</t>
+          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Pick a type of job and every number, chart and note on the page follows it.</t>
         </is>
       </c>
     </row>
@@ -615,232 +615,236 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>September 37.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Job gross margin, September · All jobs</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>Workings!B37</f>
+        <v/>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>Workings!B53</f>
+        <v/>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (October)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Job gross margin by type of job, October 2025</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C19" s="11">
-        <f>Workings!B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Installations</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>Workings!B46</f>
-        <v/>
-      </c>
-      <c r="C20" s="11">
-        <f>Workings!B45</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>Workings!B63</f>
+        <v/>
+      </c>
+      <c r="C21" s="11">
+        <f>Workings!B62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Installations</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+      <c r="C22" s="11">
+        <f>Workings!B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B21" s="8">
-        <f>Workings!B55</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>Workings!B54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B23" s="8">
+        <f>Workings!B81</f>
+        <v/>
+      </c>
+      <c r="C23" s="11">
+        <f>Workings!B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>In October maintenance contracts made a 59.5% job gross margin, installations made a 26.1% job gross margin, call-outs and repairs made a 43.3% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 52.5% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: 59.5% gross margin, the most profitable work you do. Installations: 26.1% gross margin, below the 52.5% needed to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Installations: 26.1% gross margin, 8.9 points under the 35.0% target: about $6,268 on $70,800 of revenue in October. It's below the 52.5% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in October).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Job gross margin, October · Maintenance contracts</t>
         </is>
       </c>
-      <c r="B31" s="8">
-        <f>Workings!B64</f>
-        <v/>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>September 59.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, October 2025</t>
+      <c r="B33" s="8">
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Job gross margin, September · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B34" s="8">
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wynnum medical centre</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B35" s="8">
-        <f>Workings!B77</f>
-        <v/>
-      </c>
-      <c r="C35" s="11">
-        <f>Workings!B76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B36" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C36" s="11">
-        <f>Workings!B89</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (October)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Ashgrove aged care</t>
-        </is>
-      </c>
-      <c r="B37" s="8">
-        <f>Workings!B103</f>
-        <v/>
-      </c>
-      <c r="C37" s="11">
-        <f>Workings!B102</f>
-        <v/>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, October 2025</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Fortitude Valley hotel</t>
-        </is>
-      </c>
-      <c r="B38" s="8">
-        <f>Workings!B116</f>
-        <v/>
-      </c>
-      <c r="C38" s="11">
-        <f>Workings!B115</f>
-        <v/>
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B39" s="8">
@@ -855,7 +859,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B40" s="8">
@@ -870,7 +874,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B41" s="8">
@@ -885,7 +889,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B42" s="8">
@@ -900,7 +904,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B43" s="8">
@@ -915,7 +919,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B44" s="8">
@@ -930,7 +934,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
       <c r="B45" s="8">
@@ -945,7 +949,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B46" s="8">
@@ -957,417 +961,541 @@
         <v/>
       </c>
     </row>
-    <row r="47"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B47" s="8">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C47" s="11">
+        <f>Workings!B232</f>
+        <v/>
+      </c>
+    </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B48" s="8">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C48" s="11">
+        <f>Workings!B245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B49" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C49" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+      <c r="B50" s="8">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C50" s="11">
+        <f>Workings!B271</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>The Kangaroo Point townhouses contract: 58.2% gross margin, 5.8 points clear of the 52.5% overheads need. Maintenance contracts overall: 59.5% gross margin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Job gross margin, October · Installations</t>
-        </is>
-      </c>
-      <c r="B56" s="8">
-        <f>Workings!B229</f>
-        <v/>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>September 26.2%</t>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in October). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in October).</t>
         </is>
       </c>
     </row>
     <row r="57"/>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in October 2025</t>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Installations</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr"/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Aspley cafe data cabling</t>
+          <t>Job gross margin, October · Installations</t>
         </is>
       </c>
       <c r="B60" s="8">
-        <f>Workings!B242</f>
-        <v/>
-      </c>
-      <c r="C60" s="11">
-        <f>Workings!B241</f>
-        <v/>
+        <f>Workings!B281</f>
+        <v/>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Coorparoo shop air-con install</t>
+          <t>Job gross margin, September · Installations</t>
         </is>
       </c>
       <c r="B61" s="8">
-        <f>Workings!B255</f>
-        <v/>
-      </c>
-      <c r="C61" s="11">
-        <f>Workings!B254</f>
-        <v/>
+        <f>Workings!B290</f>
+        <v/>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Salisbury shop solar and battery</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B62" s="8">
-        <f>Workings!B268</f>
-        <v/>
-      </c>
-      <c r="C62" s="11">
-        <f>Workings!B267</f>
-        <v/>
+        <f>Workings!B306</f>
+        <v/>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (October)</t>
+        </is>
       </c>
     </row>
     <row r="63"/>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>2 of the 3 installation jobs invoiced in October made less than the 35.0% job gross margin target. The Salisbury shop solar and battery made a 17.3% job gross margin: 120.0 h of technician time ($8,160) and $3,900 of subcontractors on a $35,500 job. Jobs need 52.5% gross margin just to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in October 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr"/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Aspley cafe data cabling</t>
+        </is>
+      </c>
+      <c r="B66" s="8">
+        <f>Workings!B320</f>
+        <v/>
+      </c>
+      <c r="C66" s="11">
+        <f>Workings!B319</f>
+        <v/>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="45" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Below the 52.5% overheads need: Aspley cafe data cabling (37.8%), Coorparoo shop air-con install (32.5%), Salisbury shop solar and battery (17.3%). Most profitable: Aspley cafe data cabling (37.8%).</t>
-        </is>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Coorparoo shop air-con install</t>
+        </is>
+      </c>
+      <c r="B67" s="8">
+        <f>Workings!B333</f>
+        <v/>
+      </c>
+      <c r="C67" s="11">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Salisbury shop solar and battery</t>
+        </is>
+      </c>
+      <c r="B68" s="8">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C68" s="11">
+        <f>Workings!B345</f>
+        <v/>
       </c>
     </row>
     <row r="69"/>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Job gross margin, October · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B72" s="8">
-        <f>Workings!B277</f>
-        <v/>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>September 44.0%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>2 of the 3 installation jobs invoiced in October made less than the 35.0% job gross margin target. The Salisbury shop solar and battery made a 17.3% job gross margin: 120.0 h of technician time ($8,160) and $3,900 of subcontractors on a $35,500 job. Jobs need 52.5% gross margin just to cover overheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Technician time charged, October</t>
-        </is>
-      </c>
-      <c r="B73" s="8">
-        <f>Workings!B289</f>
-        <v/>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>67.3% of call-out revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Materials charged, October</t>
-        </is>
-      </c>
-      <c r="B74" s="8">
-        <f>Workings!B301</f>
-        <v/>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>$5,610 at cost, plus 30%</t>
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2 installations under the 35.0% target, worth about $6,744 between them on $54,000 of revenue. The biggest gap, Salisbury shop solar and battery: 17.3% gross margin, 17.7 points under the 35.0% target: about $6,285 on $35,500 of revenue in October. It's below the 52.5% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
     <row r="75"/>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on call-outs by length, October 2025</t>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Call-outs and repairs</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr"/>
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1-hour call-outs (7)</t>
+          <t>Job gross margin, October · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B78" s="8">
-        <f>Workings!B314</f>
-        <v/>
-      </c>
-      <c r="C78" s="11">
-        <f>Workings!B313</f>
-        <v/>
+        <f>Workings!B355</f>
+        <v/>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1.5-hour call-outs (3)</t>
+          <t>Job gross margin, September · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B79" s="8">
-        <f>Workings!B327</f>
-        <v/>
-      </c>
-      <c r="C79" s="11">
-        <f>Workings!B326</f>
-        <v/>
+        <f>Workings!B364</f>
+        <v/>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2-hour call-outs (9)</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B80" s="8">
-        <f>Workings!B340</f>
-        <v/>
-      </c>
-      <c r="C80" s="11">
-        <f>Workings!B339</f>
-        <v/>
+        <f>Workings!B380</f>
+        <v/>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (October)</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (8)</t>
+          <t>Technician time charged, October</t>
         </is>
       </c>
       <c r="B81" s="8">
-        <f>Workings!B353</f>
-        <v/>
-      </c>
-      <c r="C81" s="11">
-        <f>Workings!B352</f>
-        <v/>
+        <f>Workings!B393</f>
+        <v/>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>67.3% of call-out revenue</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Materials charged, October</t>
+        </is>
+      </c>
+      <c r="B82" s="8">
+        <f>Workings!B405</f>
+        <v/>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>$5,610 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on call-outs by length, October 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (7)</t>
+        </is>
+      </c>
+      <c r="B86" s="8">
+        <f>Workings!B418</f>
+        <v/>
+      </c>
+      <c r="C86" s="11">
+        <f>Workings!B417</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (3)</t>
+        </is>
+      </c>
+      <c r="B87" s="8">
+        <f>Workings!B431</f>
+        <v/>
+      </c>
+      <c r="C87" s="11">
+        <f>Workings!B430</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (9)</t>
+        </is>
+      </c>
+      <c r="B88" s="8">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C88" s="11">
+        <f>Workings!B443</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (8)</t>
+        </is>
+      </c>
+      <c r="B89" s="8">
+        <f>Workings!B457</f>
+        <v/>
+      </c>
+      <c r="C89" s="11">
+        <f>Workings!B456</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>3-hour call-outs (10)</t>
         </is>
       </c>
-      <c r="B82" s="8">
-        <f>Workings!B366</f>
-        <v/>
-      </c>
-      <c r="C82" s="11">
-        <f>Workings!B365</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="B90" s="8">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C90" s="11">
+        <f>Workings!B469</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B83" s="8">
-        <f>Workings!B379</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>Workings!B378</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="B91" s="8">
+        <f>Workings!B483</f>
+        <v/>
+      </c>
+      <c r="C91" s="11">
+        <f>Workings!B482</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>43 call-outs in October billed $15,005 of technician time and $7,293 of materials ($5,610 at cost plus 30%), and made a 43.3% job gross margin between them. Gross margins run from 37.8% to 45.9% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>Call-outs: 43.3% gross margin, below the 52.5% needed to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>All call-outs: 43.3% gross margin, 8.3 points over the 35.0% target ($1,846 ahead on $22,298 in October).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
+    <row r="101"/>
+    <row r="102"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A71:D71"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A49:D49"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -1380,10 +1508,11 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="22" min="0" max="16383" man="1"/>
-    <brk id="47" min="0" max="16383" man="1"/>
-    <brk id="70" min="0" max="16383" man="1"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="18" min="0" max="16383" man="1"/>
+    <brk id="36" min="0" max="16383" man="1"/>
+    <brk id="63" min="0" max="16383" man="1"/>
+    <brk id="83" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1394,7 +1523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C382"/>
+  <dimension ref="A1:C486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1660,14 +1789,14 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts, October</t>
+          <t>All lines: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1804,12 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Oct 2025</t>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1820,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>35800</v>
+        <v>128898</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>128255</v>
       </c>
     </row>
     <row r="35">
@@ -1696,7 +1833,10 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>14516</v>
+        <v>79452</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>80054</v>
       </c>
     </row>
     <row r="36">
@@ -1709,6 +1849,10 @@
         <f>B34-B35</f>
         <v/>
       </c>
+      <c r="C36" s="13">
+        <f>C34-C35</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
@@ -1718,6 +1862,10 @@
       </c>
       <c r="B37" s="16">
         <f>B36/B34</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>C36/C34</f>
         <v/>
       </c>
     </row>
@@ -1726,14 +1874,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Installations, October</t>
+          <t>From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
@@ -1748,407 +1896,406 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Gross margin on jobs</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>70800</v>
+        <v>49446</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Technician wages and on-costs</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>52288</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B45" s="13">
-        <f>B43-B44</f>
-        <v/>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>37162</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B46" s="16">
-        <f>B45/B43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B46" s="13">
+        <f>B44-B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B47" s="13">
+        <f>B43-B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>57980</v>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Call-outs and repairs, October</t>
-        </is>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B49" s="13">
+        <f>B47-B48</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
-        </is>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
+        <v>128898</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr"/>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B51" s="14">
+        <f>B43/B50</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B52" s="14">
+        <f>B49/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B53" s="16">
+        <f>(B46+B48)/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the October 2025 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts, October</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n">
-        <v>22298</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="n">
-        <v>12648</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B54" s="13">
-        <f>B52-B53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B55" s="16">
-        <f>B54/B52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: gross margin, October and September</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Oct 25</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Sep 25</t>
-        </is>
+      <c r="B60" s="13" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>35800</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>33200</v>
+        <v>14516</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n">
-        <v>14516</v>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>13446</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B62" s="13">
+        <f>B60-B61</f>
+        <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B63" s="13">
-        <f>B61-B62</f>
-        <v/>
-      </c>
-      <c r="C63" s="13">
-        <f>C61-C62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B64" s="16">
-        <f>B63/B61</f>
-        <v/>
-      </c>
-      <c r="C64" s="16">
-        <f>C63/C61</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B63" s="16">
+        <f>B62/B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65"/>
-    <row r="66"/>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Installations, October</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+      <c r="A68" s="6" t="inlineStr"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr"/>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="n">
+        <v>70800</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B70" s="13" t="n">
-        <v>2200</v>
+        <v>52288</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="n">
-        <v>-40</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B71" s="13">
+        <f>B69-B70</f>
+        <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B72" s="16">
+        <f>B71/B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B75" s="13">
-        <f>-B73*B74</f>
-        <v/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs, October</t>
+        </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B76" s="13">
-        <f>B70+B71+B72+B75</f>
-        <v/>
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B77" s="16">
-        <f>B76/B70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79"/>
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="n">
+        <v>22298</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="n">
+        <v>12648</v>
+      </c>
+    </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Southbank cafe group</t>
-        </is>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B80" s="13">
+        <f>B78-B79</f>
+        <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr"/>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="n">
-        <v>1800</v>
-      </c>
-    </row>
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B81" s="16">
+        <f>B80/B78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83"/>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>-40</v>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts: gross margin, October and September</t>
+        </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="n">
-        <v>0</v>
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="n">
-        <v>10</v>
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>68</v>
+        <v>35800</v>
+      </c>
+      <c r="C87" s="13" t="n">
+        <v>33200</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B88" s="13">
-        <f>-B86*B87</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="n">
+        <v>14516</v>
+      </c>
+      <c r="C88" s="13" t="n">
+        <v>13446</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B89" s="13">
-        <f>B83+B84+B85+B88</f>
+        <f>B87-B88</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>C87-C88</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t>Job gross margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B90" s="16">
-        <f>B89/B83</f>
+        <f>B89/B87</f>
+        <v/>
+      </c>
+      <c r="C90" s="16">
+        <f>C89/C87</f>
         <v/>
       </c>
     </row>
@@ -2157,14 +2304,14 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Maintenance contracts: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2319,12 @@
       <c r="A95" s="6" t="inlineStr"/>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>This job</t>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
         </is>
       </c>
     </row>
@@ -2183,187 +2335,200 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>3600</v>
+        <v>35800</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>33200</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>-80</v>
+        <v>14516</v>
+      </c>
+      <c r="C97" s="13" t="n">
+        <v>13446</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="n">
-        <v>0</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B98" s="13">
+        <f>B96-B97</f>
+        <v/>
+      </c>
+      <c r="C98" s="13">
+        <f>C96-C97</f>
+        <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B100" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B101" s="13">
-        <f>-B99*B100</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B99" s="16">
+        <f>B98/B96</f>
+        <v/>
+      </c>
+      <c r="C99" s="16">
+        <f>C98/C96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101"/>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B102" s="13">
-        <f>B96+B97+B98+B101</f>
-        <v/>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, October 2025</t>
+        </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B103" s="16">
-        <f>B102/B96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105"/>
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr"/>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>49446</v>
+      </c>
+    </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Fortitude Valley hotel</t>
-        </is>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="n">
+        <v>46800</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>37162</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr"/>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B108" s="13">
+        <f>B106-B107</f>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="n">
-        <v>3400</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B109" s="13">
+        <f>B105-B108</f>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
       <c r="B110" s="13" t="n">
-        <v>-70</v>
+        <v>57980</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B111" s="13" t="n">
-        <v>0</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B111" s="13">
+        <f>B109-B110</f>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B112" s="17" t="n">
-        <v>19</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="n">
+        <v>128898</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B113" s="13" t="n">
-        <v>68</v>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B113" s="14">
+        <f>B105/B112</f>
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B114" s="13">
-        <f>-B112*B113</f>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B114" s="14">
+        <f>B111/B112</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B115" s="13">
-        <f>B109+B110+B111+B114</f>
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B115" s="16">
+        <f>(B108+B110)/B112</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B116" s="16">
-        <f>B115/B109</f>
-        <v/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the October 2025 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
       </c>
     </row>
     <row r="117"/>
@@ -2371,7 +2536,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2562,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>3200</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="123">
@@ -2407,7 +2572,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>-60</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="124">
@@ -2427,7 +2592,7 @@
         </is>
       </c>
       <c r="B125" s="17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126">
@@ -2478,7 +2643,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2669,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="136">
@@ -2514,7 +2679,7 @@
         </is>
       </c>
       <c r="B136" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="137">
@@ -2534,7 +2699,7 @@
         </is>
       </c>
       <c r="B138" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139">
@@ -2585,7 +2750,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2776,7 @@
         </is>
       </c>
       <c r="B148" s="13" t="n">
-        <v>4100</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="149">
@@ -2621,7 +2786,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-100</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="150">
@@ -2641,7 +2806,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
@@ -2692,7 +2857,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2883,7 @@
         </is>
       </c>
       <c r="B161" s="13" t="n">
-        <v>4200</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="162">
@@ -2728,7 +2893,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-90</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="163">
@@ -2748,7 +2913,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165">
@@ -2799,7 +2964,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2990,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>2800</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="175">
@@ -2855,7 +3020,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="178">
@@ -2906,7 +3071,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -2932,7 +3097,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>2600</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="188">
@@ -2942,7 +3107,7 @@
         </is>
       </c>
       <c r="B188" s="13" t="n">
-        <v>-50</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="189">
@@ -2962,7 +3127,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191">
@@ -3013,7 +3178,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3204,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>3900</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="201">
@@ -3049,7 +3214,7 @@
         </is>
       </c>
       <c r="B201" s="13" t="n">
-        <v>-110</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="202">
@@ -3069,7 +3234,7 @@
         </is>
       </c>
       <c r="B203" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204">
@@ -3120,7 +3285,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3311,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="214">
@@ -3156,7 +3321,7 @@
         </is>
       </c>
       <c r="B214" s="13" t="n">
-        <v>-50</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="215">
@@ -3176,7 +3341,7 @@
         </is>
       </c>
       <c r="B216" s="17" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="217">
@@ -3227,14 +3392,14 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, October and September</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3407,7 @@
       <c r="A225" s="6" t="inlineStr"/>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>Oct 25</t>
-        </is>
-      </c>
-      <c r="C225" s="7" t="inlineStr">
-        <is>
-          <t>Sep 25</t>
+          <t>This job</t>
         </is>
       </c>
     </row>
@@ -3258,1300 +3418,2197 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>70800</v>
-      </c>
-      <c r="C226" s="13" t="n">
-        <v>75100</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>52288</v>
-      </c>
-      <c r="C227" s="13" t="n">
-        <v>55440</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B228" s="13">
-        <f>B226-B227</f>
-        <v/>
-      </c>
-      <c r="C228" s="13">
-        <f>C226-C227</f>
-        <v/>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B228" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B229" s="16">
-        <f>B228/B226</f>
-        <v/>
-      </c>
-      <c r="C229" s="16">
-        <f>C228/C226</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230"/>
-    <row r="231"/>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B229" s="17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B230" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B231" s="13">
+        <f>-B229*B230</f>
+        <v/>
+      </c>
+    </row>
     <row r="232">
-      <c r="A232" s="5" t="inlineStr">
-        <is>
-          <t>Aspley cafe data cabling</t>
-        </is>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B232" s="13">
+        <f>B226+B227+B228+B231</f>
+        <v/>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="12" t="inlineStr">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B233" s="16">
+        <f>B232/B226</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="6" t="inlineStr"/>
-      <c r="B234" s="7" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr"/>
+      <c r="B238" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B235" s="13" t="n">
-        <v>16800</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B236" s="13" t="n">
-        <v>-4500</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B237" s="13" t="n">
-        <v>-2000</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B238" s="17" t="n">
-        <v>58</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>68</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B240" s="13">
-        <f>-B238*B239</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B240" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B241" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B242" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B243" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B244" s="13">
+        <f>-B242*B243</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B241" s="13">
-        <f>B235+B236+B237+B240</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="15" t="inlineStr">
+      <c r="B245" s="13">
+        <f>B239+B240+B241+B244</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B242" s="16">
-        <f>B241/B235</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245">
-      <c r="A245" s="5" t="inlineStr">
-        <is>
-          <t>Coorparoo shop air-con install</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="12" t="inlineStr">
+      <c r="B246" s="16">
+        <f>B245/B239</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="6" t="inlineStr"/>
-      <c r="B247" s="7" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr"/>
+      <c r="B251" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B248" s="13" t="n">
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B249" s="13" t="n">
-        <v>-6900</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B250" s="13" t="n">
-        <v>-1300</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B251" s="17" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>68</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B253" s="13">
-        <f>-B251*B252</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B253" s="13" t="n">
+        <v>-110</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B254" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B255" s="17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B257" s="13">
+        <f>-B255*B256</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B254" s="13">
-        <f>B248+B249+B250+B253</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="15" t="inlineStr">
+      <c r="B258" s="13">
+        <f>B252+B253+B254+B257</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B255" s="16">
-        <f>B254/B248</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258">
-      <c r="A258" s="5" t="inlineStr">
-        <is>
-          <t>Salisbury shop solar and battery</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="12" t="inlineStr">
+      <c r="B259" s="16">
+        <f>B258/B252</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="6" t="inlineStr"/>
-      <c r="B260" s="7" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr"/>
+      <c r="B264" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B261" s="13" t="n">
-        <v>35500</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B262" s="13" t="n">
-        <v>-17300</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B263" s="13" t="n">
-        <v>-3900</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B264" s="17" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>68</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B266" s="13">
-        <f>-B264*B265</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B266" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B267" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B268" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B269" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B270" s="13">
+        <f>-B268*B269</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B267" s="13">
-        <f>B261+B262+B263+B266</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="15" t="inlineStr">
+      <c r="B271" s="13">
+        <f>B265+B266+B267+B270</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B268" s="16">
-        <f>B267/B261</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Call-outs and repairs: gross margin, October and September</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="12" t="inlineStr">
+      <c r="B272" s="16">
+        <f>B271/B265</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>Installations: gross margin, October and September</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="12" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="6" t="inlineStr"/>
-      <c r="B273" s="7" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="6" t="inlineStr"/>
+      <c r="B277" s="7" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C273" s="7" t="inlineStr">
+      <c r="C277" s="7" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B274" s="13" t="n">
-        <v>22298</v>
-      </c>
-      <c r="C274" s="13" t="n">
-        <v>19955</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="B278" s="13" t="n">
+        <v>70800</v>
+      </c>
+      <c r="C278" s="13" t="n">
+        <v>75100</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B275" s="13" t="n">
-        <v>12648</v>
-      </c>
-      <c r="C275" s="13" t="n">
-        <v>11168</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+      <c r="B279" s="13" t="n">
+        <v>52288</v>
+      </c>
+      <c r="C279" s="13" t="n">
+        <v>55440</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B276" s="13">
-        <f>B274-B275</f>
-        <v/>
-      </c>
-      <c r="C276" s="13">
-        <f>C274-C275</f>
-        <v/>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="15" t="inlineStr">
+      <c r="B280" s="13">
+        <f>B278-B279</f>
+        <v/>
+      </c>
+      <c r="C280" s="13">
+        <f>C278-C279</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="15" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B277" s="16">
-        <f>B276/B274</f>
-        <v/>
-      </c>
-      <c r="C277" s="16">
-        <f>C276/C274</f>
-        <v/>
-      </c>
-    </row>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280">
-      <c r="A280" s="5" t="inlineStr">
-        <is>
-          <t>Call-out revenue, October</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="12" t="inlineStr">
-        <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="6" t="inlineStr"/>
-      <c r="B282" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B283" s="13" t="n">
-        <v>15005</v>
-      </c>
-    </row>
+      <c r="B281" s="16">
+        <f>B280/B278</f>
+        <v/>
+      </c>
+      <c r="C281" s="16">
+        <f>C280/C278</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282"/>
+    <row r="283"/>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B284" s="13" t="n">
-        <v>5610</v>
+      <c r="A284" s="5" t="inlineStr">
+        <is>
+          <t>Installations: gross margin, October and September</t>
+        </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B285" s="14" t="n">
-        <v>0.3</v>
+      <c r="A285" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B286" s="13">
-        <f>B284*(1+B285)</f>
-        <v/>
+      <c r="A286" s="6" t="inlineStr"/>
+      <c r="B286" s="7" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="C286" s="7" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B287" s="13" t="n">
-        <v>7293</v>
+        <v>70800</v>
+      </c>
+      <c r="C287" s="13" t="n">
+        <v>75100</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
-        </is>
-      </c>
-      <c r="B288" s="13">
-        <f>B283+B287</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B288" s="13" t="n">
+        <v>52288</v>
+      </c>
+      <c r="C288" s="13" t="n">
+        <v>55440</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B289" s="16">
-        <f>B283/B288</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290"/>
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B289" s="13">
+        <f>B287-B288</f>
+        <v/>
+      </c>
+      <c r="C289" s="13">
+        <f>C287-C288</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B290" s="16">
+        <f>B289/B287</f>
+        <v/>
+      </c>
+      <c r="C290" s="16">
+        <f>C289/C287</f>
+        <v/>
+      </c>
+    </row>
     <row r="291"/>
-    <row r="292">
-      <c r="A292" s="5" t="inlineStr">
-        <is>
-          <t>Call-out revenue, October</t>
-        </is>
-      </c>
-    </row>
+    <row r="292"/>
     <row r="293">
-      <c r="A293" s="12" t="inlineStr">
-        <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr"/>
-      <c r="B294" s="7" t="inlineStr">
+      <c r="A294" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="6" t="inlineStr"/>
+      <c r="B295" s="7" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B295" s="13" t="n">
-        <v>15005</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
+          <t>Gross margin on jobs</t>
         </is>
       </c>
       <c r="B296" s="13" t="n">
-        <v>5610</v>
+        <v>49446</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B297" s="14" t="n">
-        <v>0.3</v>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B297" s="13" t="n">
+        <v>46800</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B298" s="13">
-        <f>B296*(1+B297)</f>
-        <v/>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B298" s="13" t="n">
+        <v>37162</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
-        </is>
-      </c>
-      <c r="B299" s="13" t="n">
-        <v>7293</v>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B299" s="13">
+        <f>B297-B298</f>
+        <v/>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
+          <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
       <c r="B300" s="13">
-        <f>B295+B299</f>
+        <f>B296-B299</f>
         <v/>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B301" s="16">
-        <f>B295/B300</f>
-        <v/>
-      </c>
-    </row>
-    <row r="302"/>
-    <row r="303"/>
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B301" s="13" t="n">
+        <v>57980</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B302" s="13">
+        <f>B300-B301</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B303" s="13" t="n">
+        <v>128898</v>
+      </c>
+    </row>
     <row r="304">
-      <c r="A304" s="5" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (7)</t>
-        </is>
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B304" s="14">
+        <f>B296/B303</f>
+        <v/>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in October, added together</t>
-        </is>
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B305" s="14">
+        <f>B302/B303</f>
+        <v/>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="6" t="inlineStr"/>
-      <c r="B306" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
+      <c r="A306" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B306" s="16">
+        <f>(B299+B301)/B303</f>
+        <v/>
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B307" s="13" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B308" s="13" t="n">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B309" s="13" t="n">
-        <v>1053</v>
-      </c>
-    </row>
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the October 2025 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308"/>
+    <row r="309"/>
     <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B310" s="13">
-        <f>B308+B309</f>
-        <v/>
+      <c r="A310" s="5" t="inlineStr">
+        <is>
+          <t>Aspley cafe data cabling</t>
+        </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B311" s="13" t="n">
-        <v>-810</v>
+      <c r="A311" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B312" s="13" t="n">
-        <v>-476</v>
+      <c r="A312" s="6" t="inlineStr"/>
+      <c r="B312" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B313" s="13" t="n">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B314" s="13" t="n">
+        <v>-4500</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B315" s="13" t="n">
+        <v>-2000</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B316" s="17" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B317" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B318" s="13">
+        <f>-B316*B317</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B313" s="13">
-        <f>B310+B311+B312</f>
-        <v/>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="15" t="inlineStr">
+      <c r="B319" s="13">
+        <f>B313+B314+B315+B318</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B314" s="16">
-        <f>B313/B310</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in October, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="6" t="inlineStr"/>
-      <c r="B319" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B320" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B321" s="13" t="n">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B322" s="13" t="n">
-        <v>637</v>
-      </c>
-    </row>
+      <c r="B320" s="16">
+        <f>B319/B313</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321"/>
+    <row r="322"/>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B323" s="13">
-        <f>B321+B322</f>
-        <v/>
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Coorparoo shop air-con install</t>
+        </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B324" s="13" t="n">
-        <v>-490</v>
+      <c r="A324" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B325" s="13" t="n">
-        <v>-306</v>
+      <c r="A325" s="6" t="inlineStr"/>
+      <c r="B325" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B326" s="13" t="n">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B327" s="13" t="n">
+        <v>-6900</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B328" s="13" t="n">
+        <v>-1300</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B329" s="17" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B330" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B331" s="13">
+        <f>-B329*B330</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B326" s="13">
-        <f>B323+B324+B325</f>
-        <v/>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="15" t="inlineStr">
+      <c r="B332" s="13">
+        <f>B326+B327+B328+B331</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B327" s="16">
-        <f>B326/B323</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330">
-      <c r="A330" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in October, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="6" t="inlineStr"/>
-      <c r="B332" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B333" s="13" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B334" s="13" t="n">
-        <v>2610</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B335" s="13" t="n">
-        <v>1833</v>
-      </c>
-    </row>
+      <c r="B333" s="16">
+        <f>B332/B326</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334"/>
+    <row r="335"/>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B336" s="13">
-        <f>B334+B335</f>
-        <v/>
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t>Salisbury shop solar and battery</t>
+        </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B337" s="13" t="n">
-        <v>-1410</v>
+      <c r="A337" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B338" s="13" t="n">
-        <v>-1224</v>
+      <c r="A338" s="6" t="inlineStr"/>
+      <c r="B338" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B339" s="13" t="n">
+        <v>35500</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B340" s="13" t="n">
+        <v>-17300</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B341" s="13" t="n">
+        <v>-3900</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B342" s="17" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B343" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B344" s="13">
+        <f>-B342*B343</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B339" s="13">
-        <f>B336+B337+B338</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="15" t="inlineStr">
+      <c r="B345" s="13">
+        <f>B339+B340+B341+B344</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B340" s="16">
-        <f>B339/B336</f>
-        <v/>
-      </c>
-    </row>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343">
-      <c r="A343" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in October, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="6" t="inlineStr"/>
-      <c r="B345" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B346" s="13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B347" s="13" t="n">
-        <v>2899</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B348" s="13" t="n">
-        <v>1235</v>
-      </c>
-    </row>
+      <c r="B346" s="16">
+        <f>B345/B339</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347"/>
+    <row r="348"/>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B349" s="13">
-        <f>B347+B348</f>
-        <v/>
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, October and September</t>
+        </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B350" s="13" t="n">
-        <v>-950</v>
+      <c r="A350" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B351" s="13" t="n">
-        <v>-1360</v>
+      <c r="A351" s="6" t="inlineStr"/>
+      <c r="B351" s="7" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="C351" s="7" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B352" s="13">
-        <f>B349+B350+B351</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B352" s="13" t="n">
+        <v>22298</v>
+      </c>
+      <c r="C352" s="13" t="n">
+        <v>19955</v>
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B353" s="16">
-        <f>B352/B349</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356">
-      <c r="A356" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in October, added together</t>
-        </is>
-      </c>
-    </row>
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B353" s="13" t="n">
+        <v>12648</v>
+      </c>
+      <c r="C353" s="13" t="n">
+        <v>11168</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B354" s="13">
+        <f>B352-B353</f>
+        <v/>
+      </c>
+      <c r="C354" s="13">
+        <f>C352-C353</f>
+        <v/>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B355" s="16">
+        <f>B354/B352</f>
+        <v/>
+      </c>
+      <c r="C355" s="16">
+        <f>C354/C352</f>
+        <v/>
+      </c>
+    </row>
+    <row r="356"/>
+    <row r="357"/>
     <row r="358">
-      <c r="A358" s="6" t="inlineStr"/>
-      <c r="B358" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
+      <c r="A358" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B359" s="13" t="n">
-        <v>10</v>
+      <c r="A359" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B360" s="13" t="n">
-        <v>4350</v>
+      <c r="A360" s="6" t="inlineStr"/>
+      <c r="B360" s="7" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="C360" s="7" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B361" s="13" t="n">
-        <v>1430</v>
+        <v>22298</v>
+      </c>
+      <c r="C361" s="13" t="n">
+        <v>19955</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B362" s="13">
-        <f>B360+B361</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B362" s="13" t="n">
+        <v>12648</v>
+      </c>
+      <c r="C362" s="13" t="n">
+        <v>11168</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B363" s="13" t="n">
-        <v>-1100</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B363" s="13">
+        <f>B361-B362</f>
+        <v/>
+      </c>
+      <c r="C363" s="13">
+        <f>C361-C362</f>
+        <v/>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B364" s="13" t="n">
-        <v>-2040</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B365" s="13">
-        <f>B362+B363+B364</f>
-        <v/>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B366" s="16">
-        <f>B365/B362</f>
-        <v/>
-      </c>
-    </row>
-    <row r="367"/>
-    <row r="368"/>
+      <c r="A364" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B364" s="16">
+        <f>B363/B361</f>
+        <v/>
+      </c>
+      <c r="C364" s="16">
+        <f>C363/C361</f>
+        <v/>
+      </c>
+    </row>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367">
+      <c r="A367" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, October 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
     <row r="369">
-      <c r="A369" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (6)</t>
+      <c r="A369" s="6" t="inlineStr"/>
+      <c r="B369" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in October, added together</t>
-        </is>
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B370" s="13" t="n">
+        <v>49446</v>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="6" t="inlineStr"/>
-      <c r="B371" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B371" s="13" t="n">
+        <v>46800</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
       <c r="B372" s="13" t="n">
-        <v>6</v>
+        <v>37162</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B373" s="13" t="n">
-        <v>3480</v>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B373" s="13">
+        <f>B371-B372</f>
+        <v/>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B374" s="13" t="n">
-        <v>1105</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B374" s="13">
+        <f>B370-B373</f>
+        <v/>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B375" s="13">
-        <f>B373+B374</f>
-        <v/>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B375" s="13" t="n">
+        <v>57980</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B376" s="13" t="n">
-        <v>-850</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B376" s="13">
+        <f>B374-B375</f>
+        <v/>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B377" s="13" t="n">
-        <v>-1632</v>
+        <v>128898</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B378" s="14">
+        <f>B370/B377</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B379" s="14">
+        <f>B376/B377</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B380" s="16">
+        <f>(B373+B375)/B377</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the October 2025 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384">
+      <c r="A384" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, October</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="6" t="inlineStr"/>
+      <c r="B386" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B387" s="13" t="n">
+        <v>15005</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B388" s="13" t="n">
+        <v>5610</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B389" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B390" s="13">
+        <f>B388*(1+B389)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B391" s="13" t="n">
+        <v>7293</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B392" s="13">
+        <f>B387+B391</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B393" s="16">
+        <f>B387/B392</f>
+        <v/>
+      </c>
+    </row>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396">
+      <c r="A396" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, October</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="6" t="inlineStr"/>
+      <c r="B398" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B399" s="13" t="n">
+        <v>15005</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B400" s="13" t="n">
+        <v>5610</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B401" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B402" s="13">
+        <f>B400*(1+B401)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B403" s="13" t="n">
+        <v>7293</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B404" s="13">
+        <f>B399+B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B405" s="16">
+        <f>B399/B404</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408">
+      <c r="A408" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in October, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="6" t="inlineStr"/>
+      <c r="B410" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B411" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B412" s="13" t="n">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B413" s="13" t="n">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B414" s="13">
+        <f>B412+B413</f>
+        <v/>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B415" s="13" t="n">
+        <v>-810</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B416" s="13" t="n">
+        <v>-476</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B378" s="13">
-        <f>B375+B376+B377</f>
-        <v/>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="15" t="inlineStr">
+      <c r="B417" s="13">
+        <f>B414+B415+B416</f>
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B379" s="16">
-        <f>B378/B375</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
+      <c r="B418" s="16">
+        <f>B417/B414</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421">
+      <c r="A421" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in October, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="6" t="inlineStr"/>
+      <c r="B423" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B424" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B425" s="13" t="n">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B426" s="13" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B427" s="13">
+        <f>B425+B426</f>
+        <v/>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B428" s="13" t="n">
+        <v>-490</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B429" s="13" t="n">
+        <v>-306</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B430" s="13">
+        <f>B427+B428+B429</f>
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B431" s="16">
+        <f>B430/B427</f>
+        <v/>
+      </c>
+    </row>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434">
+      <c r="A434" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in October, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="inlineStr"/>
+      <c r="B436" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B437" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B438" s="13" t="n">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B439" s="13" t="n">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B440" s="13">
+        <f>B438+B439</f>
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B441" s="13" t="n">
+        <v>-1410</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B442" s="13" t="n">
+        <v>-1224</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B443" s="13">
+        <f>B440+B441+B442</f>
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B444" s="16">
+        <f>B443/B440</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447">
+      <c r="A447" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in October, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="6" t="inlineStr"/>
+      <c r="B449" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B450" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B451" s="13" t="n">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B452" s="13" t="n">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B453" s="13">
+        <f>B451+B452</f>
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B454" s="13" t="n">
+        <v>-950</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B455" s="13" t="n">
+        <v>-1360</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B456" s="13">
+        <f>B453+B454+B455</f>
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B457" s="16">
+        <f>B456/B453</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460">
+      <c r="A460" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in October, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="6" t="inlineStr"/>
+      <c r="B462" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B463" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B464" s="13" t="n">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B465" s="13" t="n">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B466" s="13">
+        <f>B464+B465</f>
+        <v/>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B467" s="13" t="n">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B468" s="13" t="n">
+        <v>-2040</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B469" s="13">
+        <f>B466+B467+B468</f>
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B470" s="16">
+        <f>B469/B466</f>
+        <v/>
+      </c>
+    </row>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in October, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="6" t="inlineStr"/>
+      <c r="B475" s="7" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B476" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B477" s="13" t="n">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B478" s="13" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B479" s="13">
+        <f>B477+B478</f>
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B480" s="13" t="n">
+        <v>-850</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B481" s="13" t="n">
+        <v>-1632</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B482" s="13">
+        <f>B479+B480+B481</f>
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B483" s="16">
+        <f>B482/B479</f>
+        <v/>
+      </c>
+    </row>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4564,21 +5621,25 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="14" manualBreakCount="14">
+  <rowBreaks count="18" manualBreakCount="18">
     <brk id="30" min="0" max="16383" man="1"/>
-    <brk id="57" min="0" max="16383" man="1"/>
-    <brk id="79" min="0" max="16383" man="1"/>
-    <brk id="105" min="0" max="16383" man="1"/>
+    <brk id="56" min="0" max="16383" man="1"/>
+    <brk id="83" min="0" max="16383" man="1"/>
+    <brk id="101" min="0" max="16383" man="1"/>
     <brk id="131" min="0" max="16383" man="1"/>
     <brk id="157" min="0" max="16383" man="1"/>
     <brk id="183" min="0" max="16383" man="1"/>
     <brk id="209" min="0" max="16383" man="1"/>
-    <brk id="231" min="0" max="16383" man="1"/>
-    <brk id="257" min="0" max="16383" man="1"/>
-    <brk id="279" min="0" max="16383" man="1"/>
-    <brk id="303" min="0" max="16383" man="1"/>
-    <brk id="329" min="0" max="16383" man="1"/>
-    <brk id="355" min="0" max="16383" man="1"/>
+    <brk id="235" min="0" max="16383" man="1"/>
+    <brk id="261" min="0" max="16383" man="1"/>
+    <brk id="292" min="0" max="16383" man="1"/>
+    <brk id="322" min="0" max="16383" man="1"/>
+    <brk id="348" min="0" max="16383" man="1"/>
+    <brk id="366" min="0" max="16383" man="1"/>
+    <brk id="395" min="0" max="16383" man="1"/>
+    <brk id="420" min="0" max="16383" man="1"/>
+    <brk id="446" min="0" max="16383" man="1"/>
+    <brk id="472" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2025-10/job-margins.xlsx
+++ b/media/exports/reports/2025-10/job-margins.xlsx
@@ -12,7 +12,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Job_gross_margin_October_All_jobs">'Report'!$B$15</definedName>
+    <definedName name="Job_gross_margin_September_All_jobs">'Report'!$B$16</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$17</definedName>
+    <definedName name="Job_gross_margin_October_Maintenance_contracts">'Report'!$B$41</definedName>
+    <definedName name="Job_gross_margin_September_Maintenance_contracts">'Report'!$B$42</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$43</definedName>
+    <definedName name="Job_gross_margin_October_Installations">'Report'!$B$77</definedName>
+    <definedName name="Job_gross_margin_September_Installations">'Report'!$B$78</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$79</definedName>
+    <definedName name="Job_gross_margin_October_Call_outs_and_repairs">'Report'!$B$103</definedName>
+    <definedName name="Job_gross_margin_September_Call_outs_and_repairs">'Report'!$B$104</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$105</definedName>
+    <definedName name="Technician_time_charged_October">'Report'!$B$106</definedName>
+    <definedName name="Materials_charged_October">'Report'!$B$107</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$132</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$483</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,11 +67,6 @@
       <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
@@ -70,6 +82,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="002F7A5D"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -118,27 +135,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,6 +238,820 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin by type of job, October 2025 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$21:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$21:$B$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each maintenance contract, October 2025 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$47:$A$58</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$47:$B$58</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each installation invoiced in October 2025 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$83:$A$85</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$83:$B$85</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on call-outs by length, October 2025 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$111:$A$116</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$111:$B$116</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Revenue by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>All</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$6:$D$18</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Maintenance contracts</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$19:$D$31</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Installations</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$32:$D$44</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Call-outs and repairs</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5F6F63"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$45:$D$57</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>81</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="job_margins_Data" displayName="job_margins_Data" ref="A5:G57" headerRowCount="1">
+  <autoFilter ref="A5:G57"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Direct cost"/>
+    <tableColumn id="6" name="Gross margin"/>
+    <tableColumn id="7" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -510,7 +1343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -529,14 +1362,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -552,14 +1385,14 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Gross margin, not profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>From gross margin to profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>October's jobs made $49,446 gross margin (38.4%). Technician time not charged to jobs took $9,638 and overheads $57,980, leaving ($18,172) profit before tax ((14.1%) of revenue). To cover overheads, jobs need a 52.5% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -567,14 +1400,14 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>From gross margin to profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Gross margin, not profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>October's jobs made $49,446 gross margin (38.4%). Technician time not charged to jobs took $9,638 and overheads $57,980, leaving ($18,172) profit before tax ((14.1%) of revenue). To cover overheads, jobs need a 52.5% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
         </is>
       </c>
     </row>
@@ -718,541 +1551,405 @@
       </c>
     </row>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>In October maintenance contracts made a 59.5% job gross margin, installations made a 26.1% job gross margin, call-outs and repairs made a 43.3% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 52.5% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Installations: 26.1% gross margin, 8.9 points under the 35.0% target: about $6,268 on $70,800 of revenue in October. It's below the 52.5% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in October).</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Job gross margin, October · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B33" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Job gross margin, September · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B34" s="8">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B35" s="8">
-        <f>Workings!B115</f>
-        <v/>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (October)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, October 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B39" s="8">
-        <f>Workings!B129</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>Workings!B128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B40" s="8">
-        <f>Workings!B142</f>
-        <v/>
-      </c>
-      <c r="C40" s="11">
-        <f>Workings!B141</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Job gross margin, October · Maintenance contracts</t>
         </is>
       </c>
       <c r="B41" s="8">
-        <f>Workings!B155</f>
-        <v/>
-      </c>
-      <c r="C41" s="11">
-        <f>Workings!B154</f>
-        <v/>
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Job gross margin, September · Maintenance contracts</t>
         </is>
       </c>
       <c r="B42" s="8">
-        <f>Workings!B168</f>
-        <v/>
-      </c>
-      <c r="C42" s="11">
-        <f>Workings!B167</f>
-        <v/>
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B43" s="8">
-        <f>Workings!B181</f>
-        <v/>
-      </c>
-      <c r="C43" s="11">
-        <f>Workings!B180</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Newstead gym</t>
-        </is>
-      </c>
-      <c r="B44" s="8">
-        <f>Workings!B194</f>
-        <v/>
-      </c>
-      <c r="C44" s="11">
-        <f>Workings!B193</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (October)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Chermside retail centre</t>
-        </is>
-      </c>
-      <c r="B45" s="8">
-        <f>Workings!B207</f>
-        <v/>
-      </c>
-      <c r="C45" s="11">
-        <f>Workings!B206</f>
-        <v/>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, October 2025</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Milton office tower</t>
-        </is>
-      </c>
-      <c r="B46" s="8">
-        <f>Workings!B220</f>
-        <v/>
-      </c>
-      <c r="C46" s="11">
-        <f>Workings!B219</f>
-        <v/>
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B47" s="8">
-        <f>Workings!B233</f>
+        <f>Workings!B129</f>
         <v/>
       </c>
       <c r="C47" s="11">
-        <f>Workings!B232</f>
+        <f>Workings!B128</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B48" s="8">
-        <f>Workings!B246</f>
+        <f>Workings!B142</f>
         <v/>
       </c>
       <c r="C48" s="11">
-        <f>Workings!B245</f>
+        <f>Workings!B141</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B49" s="8">
-        <f>Workings!B259</f>
+        <f>Workings!B155</f>
         <v/>
       </c>
       <c r="C49" s="11">
-        <f>Workings!B258</f>
+        <f>Workings!B154</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Fortitude Valley hotel</t>
+        </is>
+      </c>
+      <c r="B50" s="8">
+        <f>Workings!B168</f>
+        <v/>
+      </c>
+      <c r="C50" s="11">
+        <f>Workings!B167</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Riverside Apartments (strata)</t>
+        </is>
+      </c>
+      <c r="B51" s="8">
+        <f>Workings!B181</f>
+        <v/>
+      </c>
+      <c r="C51" s="11">
+        <f>Workings!B180</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Newstead gym</t>
+        </is>
+      </c>
+      <c r="B52" s="8">
+        <f>Workings!B194</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>Workings!B193</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chermside retail centre</t>
+        </is>
+      </c>
+      <c r="B53" s="8">
+        <f>Workings!B207</f>
+        <v/>
+      </c>
+      <c r="C53" s="11">
+        <f>Workings!B206</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Milton office tower</t>
+        </is>
+      </c>
+      <c r="B54" s="8">
+        <f>Workings!B220</f>
+        <v/>
+      </c>
+      <c r="C54" s="11">
+        <f>Workings!B219</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B55" s="8">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C55" s="11">
+        <f>Workings!B232</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B56" s="8">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C56" s="11">
+        <f>Workings!B245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B57" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C57" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B50" s="8">
+      <c r="B58" s="8">
         <f>Workings!B272</f>
         <v/>
       </c>
-      <c r="C50" s="11">
+      <c r="C58" s="11">
         <f>Workings!B271</f>
         <v/>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in October). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in October).</t>
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>Type of job: Installations</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Job gross margin, October · Installations</t>
         </is>
       </c>
-      <c r="B60" s="8">
+      <c r="B77" s="8">
         <f>Workings!B281</f>
         <v/>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Job gross margin, September · Installations</t>
-        </is>
-      </c>
-      <c r="B61" s="8">
-        <f>Workings!B290</f>
-        <v/>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B62" s="8">
-        <f>Workings!B306</f>
-        <v/>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (October)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in October 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr"/>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Aspley cafe data cabling</t>
-        </is>
-      </c>
-      <c r="B66" s="8">
-        <f>Workings!B320</f>
-        <v/>
-      </c>
-      <c r="C66" s="11">
-        <f>Workings!B319</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Coorparoo shop air-con install</t>
-        </is>
-      </c>
-      <c r="B67" s="8">
-        <f>Workings!B333</f>
-        <v/>
-      </c>
-      <c r="C67" s="11">
-        <f>Workings!B332</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Salisbury shop solar and battery</t>
-        </is>
-      </c>
-      <c r="B68" s="8">
-        <f>Workings!B346</f>
-        <v/>
-      </c>
-      <c r="C68" s="11">
-        <f>Workings!B345</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>2 of the 3 installation jobs invoiced in October made less than the 35.0% job gross margin target. The Salisbury shop solar and battery made a 17.3% job gross margin: 120.0 h of technician time ($8,160) and $3,900 of subcontractors on a $35,500 job. Jobs need 52.5% gross margin just to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>2 installations under the 35.0% target, worth about $6,744 between them on $54,000 of revenue. The biggest gap, Salisbury shop solar and battery: 17.3% gross margin, 17.7 points under the 35.0% target: about $6,285 on $35,500 of revenue in October. It's below the 52.5% needed to cover overheads, too.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Job gross margin, October · Call-outs and repairs</t>
+          <t>Job gross margin, September · Installations</t>
         </is>
       </c>
       <c r="B78" s="8">
-        <f>Workings!B355</f>
+        <f>Workings!B290</f>
         <v/>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -1264,256 +1961,426 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B79" s="8">
+        <f>Workings!B306</f>
+        <v/>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (October)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in October 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr"/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Aspley cafe data cabling</t>
+        </is>
+      </c>
+      <c r="B83" s="8">
+        <f>Workings!B320</f>
+        <v/>
+      </c>
+      <c r="C83" s="11">
+        <f>Workings!B319</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Coorparoo shop air-con install</t>
+        </is>
+      </c>
+      <c r="B84" s="8">
+        <f>Workings!B333</f>
+        <v/>
+      </c>
+      <c r="C84" s="11">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Salisbury shop solar and battery</t>
+        </is>
+      </c>
+      <c r="B85" s="8">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C85" s="11">
+        <f>Workings!B345</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>2 of the 3 installation jobs invoiced in October made less than the 35.0% job gross margin target. The Salisbury shop solar and battery made a 17.3% job gross margin: 120.0 h of technician time ($8,160) and $3,900 of subcontractors on a $35,500 job. Jobs need 52.5% gross margin just to cover overheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2 installations under the 35.0% target, worth about $6,744 between them on $54,000 of revenue. The biggest gap, Salisbury shop solar and battery: 17.3% gross margin, 17.7 points under the 35.0% target: about $6,285 on $35,500 of revenue in October. It's below the 52.5% needed to cover overheads, too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Call-outs and repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Compared with</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Job gross margin, October · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B103" s="8">
+        <f>Workings!B355</f>
+        <v/>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>Job gross margin, September · Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B79" s="8">
+      <c r="B104" s="8">
         <f>Workings!B364</f>
         <v/>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B80" s="8">
+      <c r="B105" s="8">
         <f>Workings!B380</f>
         <v/>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (October)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>Technician time charged, October</t>
         </is>
       </c>
-      <c r="B81" s="8">
+      <c r="B106" s="8">
         <f>Workings!B393</f>
         <v/>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C106" s="9" t="inlineStr">
         <is>
           <t>67.3% of call-out revenue</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>Materials charged, October</t>
         </is>
       </c>
-      <c r="B82" s="8">
+      <c r="B107" s="8">
         <f>Workings!B405</f>
         <v/>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>$5,610 at cost, plus 30%</t>
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, October 2025</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr"/>
-      <c r="B85" s="7" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr"/>
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>1-hour call-outs (7)</t>
         </is>
       </c>
-      <c r="B86" s="8">
+      <c r="B111" s="8">
         <f>Workings!B418</f>
         <v/>
       </c>
-      <c r="C86" s="11">
+      <c r="C111" s="11">
         <f>Workings!B417</f>
         <v/>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>1.5-hour call-outs (3)</t>
         </is>
       </c>
-      <c r="B87" s="8">
+      <c r="B112" s="8">
         <f>Workings!B431</f>
         <v/>
       </c>
-      <c r="C87" s="11">
+      <c r="C112" s="11">
         <f>Workings!B430</f>
         <v/>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>2-hour call-outs (9)</t>
         </is>
       </c>
-      <c r="B88" s="8">
+      <c r="B113" s="8">
         <f>Workings!B444</f>
         <v/>
       </c>
-      <c r="C88" s="11">
+      <c r="C113" s="11">
         <f>Workings!B443</f>
         <v/>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>2.5-hour call-outs (8)</t>
         </is>
       </c>
-      <c r="B89" s="8">
+      <c r="B114" s="8">
         <f>Workings!B457</f>
         <v/>
       </c>
-      <c r="C89" s="11">
+      <c r="C114" s="11">
         <f>Workings!B456</f>
         <v/>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>3-hour call-outs (10)</t>
         </is>
       </c>
-      <c r="B90" s="8">
+      <c r="B115" s="8">
         <f>Workings!B470</f>
         <v/>
       </c>
-      <c r="C90" s="11">
+      <c r="C115" s="11">
         <f>Workings!B469</f>
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B91" s="8">
+      <c r="B116" s="8">
         <f>Workings!B483</f>
         <v/>
       </c>
-      <c r="C91" s="11">
+      <c r="C116" s="11">
         <f>Workings!B482</f>
         <v/>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>43 call-outs in October billed $15,005 of technician time and $7,293 of materials ($5,610 at cost plus 30%), and made a 43.3% job gross margin between them. Gross margins run from 37.8% to 45.9% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>All call-outs: 43.3% gross margin, 8.3 points over the 35.0% target ($1,846 ahead on $22,298 in October).</t>
         </is>
       </c>
     </row>
-    <row r="98"/>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="12" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="101"/>
-    <row r="102"/>
+    <row r="133"/>
+    <row r="134"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A126:D126"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A129:D129"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A99:D99"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="4" manualBreakCount="4">
+  <rowBreaks count="5" manualBreakCount="5">
     <brk id="18" min="0" max="16383" man="1"/>
-    <brk id="36" min="0" max="16383" man="1"/>
-    <brk id="63" min="0" max="16383" man="1"/>
-    <brk id="83" min="0" max="16383" man="1"/>
+    <brk id="44" min="0" max="16383" man="1"/>
+    <brk id="68" min="0" max="16383" man="1"/>
+    <brk id="94" min="0" max="16383" man="1"/>
+    <brk id="108" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1542,14 +2409,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1557,7 +2424,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, October 2025</t>
+          <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
@@ -1704,7 +2571,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, October and September</t>
+          <t>Trades, all lines: gross margin, October and September</t>
         </is>
       </c>
     </row>
@@ -1789,7 +2656,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, October and September</t>
+          <t>Trades, all lines: gross margin, October and September</t>
         </is>
       </c>
     </row>
@@ -1874,7 +2741,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, October 2025</t>
+          <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
@@ -2219,7 +3086,7 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, October and September</t>
+          <t>Trades, Maintenance contracts: gross margin, October and September</t>
         </is>
       </c>
     </row>
@@ -2304,7 +3171,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, October and September</t>
+          <t>Trades, Maintenance contracts: gross margin, October and September</t>
         </is>
       </c>
     </row>
@@ -2389,7 +3256,7 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, October 2025</t>
+          <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
@@ -3820,7 +4687,7 @@
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, October and September</t>
+          <t>Trades, Installations: gross margin, October and September</t>
         </is>
       </c>
     </row>
@@ -3905,7 +4772,7 @@
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, October and September</t>
+          <t>Trades, Installations: gross margin, October and September</t>
         </is>
       </c>
     </row>
@@ -3990,7 +4857,7 @@
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, October 2025</t>
+          <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
@@ -4458,7 +5325,7 @@
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, October and September</t>
+          <t>Trades, Call-outs and repairs: gross margin, October and September</t>
         </is>
       </c>
     </row>
@@ -4543,7 +5410,7 @@
     <row r="358">
       <c r="A358" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, October and September</t>
+          <t>Trades, Call-outs and repairs: gross margin, October and September</t>
         </is>
       </c>
     </row>
@@ -4628,7 +5495,7 @@
     <row r="367">
       <c r="A367" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, October 2025</t>
+          <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
@@ -5615,7 +6482,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5672,14 +6539,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -7339,7 +8206,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7348,5 +8215,9 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="31" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2025-10/job-margins.xlsx
+++ b/media/exports/reports/2025-10/job-margins.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart lines" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Job_gross_margin_October_All_jobs">'Report'!$B$15</definedName>
@@ -28,8 +29,8 @@
     <definedName name="Materials_charged_October">'Report'!$B$107</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$132</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$483</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$57</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -264,7 +265,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin by type of job, October 2025 · target 35.0%</a:t>
+              <a:t>Job gross margin by type of job, October 2025</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -331,6 +332,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$4:$B$5</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$4:$C$5</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 52.5%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$8:$B$9</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$8:$C$9</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -346,6 +495,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.6842499999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -353,6 +504,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.6842499999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -385,7 +563,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each maintenance contract, October 2025 · target 35.0%</a:t>
+              <a:t>Job gross margin on each maintenance contract, October 2025</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -438,6 +616,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$12:$B$13</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$12:$C$13</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 52.5%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$16:$B$17</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$16:$C$17</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -453,6 +779,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.7026499999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -460,6 +788,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.7026499999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -492,7 +847,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each installation invoiced in October 2025 · target 35.0%</a:t>
+              <a:t>Job gross margin on each installation invoiced in October 2025</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -573,6 +928,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$20:$B$21</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$20:$C$21</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 52.5%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$24:$B$25</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$24:$C$25</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -588,6 +1091,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.60375"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -595,6 +1100,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.60375"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -627,7 +1159,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on call-outs by length, October 2025 · target 35.0%</a:t>
+              <a:t>Job gross margin on call-outs by length, October 2025</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -680,6 +1212,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$28:$B$29</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$28:$C$29</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 52.5%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$32:$B$33</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$32:$C$33</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -695,6 +1375,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.60375"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -702,6 +1384,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.60375"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -927,7 +1636,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="1980000"/>
+    <ext cx="5400000" cy="2196000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -949,7 +1658,7 @@
       <row>45</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3960000"/>
+    <ext cx="5400000" cy="4176000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -971,7 +1680,7 @@
       <row>81</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="1980000"/>
+    <ext cx="5400000" cy="2196000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -993,7 +1702,7 @@
       <row>109</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2340000"/>
+    <ext cx="5400000" cy="2556000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1369,7 +2078,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -2367,7 +3076,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2416,7 +3125,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -6482,7 +7191,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6515,6 +7224,219 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Points for the target and break-even lines drawn on the charts (hidden sheet; edit the values on the chart's own sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, October 2025: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, October 2025: Break-even 52.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, October 2025: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, October 2025: Break-even 52.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in October 2025: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in October 2025: Break-even 52.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, October 2025: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, October 2025: Break-even 52.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G57"/>
@@ -6546,7 +7468,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -8206,7 +9128,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2025-10/job-margins.xlsx
+++ b/media/exports/reports/2025-10/job-margins.xlsx
@@ -409,7 +409,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 52.5%</v>
+            <v>Break-even 62.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -495,7 +495,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6842499999999999"/>
+          <max val="0.7336999999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -509,7 +509,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6842499999999999"/>
+          <max val="0.7336999999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -693,7 +693,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 52.5%</v>
+            <v>Break-even 62.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -779,7 +779,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7026499999999999"/>
+          <max val="0.7486499999999998"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -793,7 +793,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7026499999999999"/>
+          <max val="0.7486499999999998"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -877,20 +877,6 @@
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dPt>
             <idx val="2"/>
             <spPr>
@@ -1005,7 +991,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 52.5%</v>
+            <v>Break-even 62.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1091,7 +1077,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.60375"/>
+          <max val="0.713"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1105,7 +1091,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.60375"/>
+          <max val="0.713"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1289,7 +1275,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 52.5%</v>
+            <v>Break-even 62.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1375,7 +1361,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.60375"/>
+          <max val="0.713"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1389,7 +1375,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.60375"/>
+          <max val="0.713"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -2078,7 +2064,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2087,7 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>October's jobs made $49,446 gross margin (38.4%). Technician time not charged to jobs took $9,638 and overheads $57,980, leaving ($18,172) profit before tax ((14.1%) of revenue). To cover overheads, jobs need a 52.5% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>October's jobs made $64,114 gross margin (44.7%). Technician time not charged to jobs took $31,056 and overheads $57,980, leaving ($24,922) profit before tax ((17.4%) of revenue). To cover overheads, jobs need a 62.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2102,7 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2264,7 @@
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>In October maintenance contracts made a 59.5% job gross margin, installations made a 26.1% job gross margin, call-outs and repairs made a 43.3% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 52.5% just to cover overheads.</t>
+          <t>In October maintenance contracts made a 63.8% job gross margin, installations made a 34.1% job gross margin, call-outs and repairs made a 47.7% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 62.0% just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2279,7 @@
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Installations: 26.1% gross margin, 8.9 points under the 35.0% target: about $6,268 on $70,800 of revenue in October. It's below the 52.5% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in October).</t>
+          <t>Installations: 34.1% gross margin, 0.9 points under the 35.0% target: about $743 on $79,300 of revenue in October. It's below the 62.0% needed to cover overheads, too. Maintenance contracts: 63.8% gross margin, 28.8 points over the 35.0% target ($11,549 ahead on $40,100 in October).</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2395,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B48" s="8">
@@ -2424,7 +2410,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B49" s="8">
@@ -2439,7 +2425,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B50" s="8">
@@ -2454,7 +2440,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B51" s="8">
@@ -2469,7 +2455,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B52" s="8">
@@ -2499,7 +2485,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Bulimba school</t>
         </is>
       </c>
       <c r="B54" s="8">
@@ -2514,7 +2500,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -2591,7 +2577,7 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
+          <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 62.9% job gross margin: 14.0 h of technician time on a $2,700 monthly fee.</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2592,7 @@
     <row r="73" ht="45" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in October). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in October).</t>
+          <t>The thinnest, Kangaroo Point townhouses: 62.9% gross margin, 27.9 points over the 35.0% target ($753 ahead on $2,700 in October). All maintenance contracts: 63.8% gross margin, 28.8 points over the 35.0% target ($11,549 ahead on $40,100 in October).</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2754,7 @@
     <row r="96" ht="60" customHeight="1">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2 of the 3 installation jobs invoiced in October made less than the 35.0% job gross margin target. The Salisbury shop solar and battery made a 17.3% job gross margin: 120.0 h of technician time ($8,160) and $3,900 of subcontractors on a $35,500 job. Jobs need 52.5% gross margin just to cover overheads.</t>
+          <t>1 of the 3 installation jobs invoiced in October made less than the 35.0% job gross margin target. The Salisbury shop solar and battery made a 26.2% job gross margin: 120.0 h of technician time ($8,160) and $3,900 of subcontractors on a $39,800 job. Jobs need 62.0% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2769,7 @@
     <row r="99" ht="60" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2 installations under the 35.0% target, worth about $6,744 between them on $54,000 of revenue. The biggest gap, Salisbury shop solar and battery: 17.3% gross margin, 17.7 points under the 35.0% target: about $6,285 on $35,500 of revenue in October. It's below the 52.5% needed to cover overheads, too.</t>
+          <t>1 installation under the 35.0% target, worth about $3,490 between them on $39,800 of revenue. The biggest gap, Salisbury shop solar and battery: 26.2% gross margin, 8.8 points under the 35.0% target: about $3,490 on $39,800 of revenue in October. It's below the 62.0% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2858,7 @@
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>67.3% of call-out revenue</t>
+          <t>69.8% of call-out revenue</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3007,7 @@
     <row r="126" ht="60" customHeight="1">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>43 call-outs in October billed $15,005 of technician time and $7,293 of materials ($5,610 at cost plus 30%), and made a 43.3% job gross margin between them. Gross margins run from 37.8% to 45.9% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+          <t>43 call-outs in October billed $16,873 of technician time and $7,293 of materials ($5,610 at cost plus 30%), and made a 47.7% job gross margin between them. Gross margins run from 41.4% to 50.5% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3022,7 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>All call-outs: 43.3% gross margin, 8.3 points over the 35.0% target ($1,846 ahead on $22,298 in October).</t>
+          <t>All call-outs: 47.7% gross margin, 12.7 points over the 35.0% target ($3,060 ahead on $24,166 in October).</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3062,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3125,7 +3111,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3145,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>49446</v>
+        <v>64114</v>
       </c>
     </row>
     <row r="9">
@@ -3169,7 +3155,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>46800</v>
+        <v>68218</v>
       </c>
     </row>
     <row r="10">
@@ -3232,7 +3218,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
     </row>
     <row r="16">
@@ -3271,7 +3257,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the October 2025 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the October 2025 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3311,10 +3297,10 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
     </row>
     <row r="26">
@@ -3396,10 +3382,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
     </row>
     <row r="35">
@@ -3476,7 +3462,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>49446</v>
+        <v>64114</v>
       </c>
     </row>
     <row r="44">
@@ -3486,7 +3472,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>46800</v>
+        <v>68218</v>
       </c>
     </row>
     <row r="45">
@@ -3549,7 +3535,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
     </row>
     <row r="51">
@@ -3588,7 +3574,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Ties to the October 2025 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the October 2025 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3609,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
     </row>
     <row r="61">
@@ -3689,7 +3675,7 @@
         </is>
       </c>
       <c r="B69" s="13" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="70">
@@ -3755,7 +3741,7 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
     </row>
     <row r="79">
@@ -3826,10 +3812,10 @@
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="88">
@@ -3911,10 +3897,10 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="C96" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="97">
@@ -3991,7 +3977,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>49446</v>
+        <v>64114</v>
       </c>
     </row>
     <row r="106">
@@ -4001,7 +3987,7 @@
         </is>
       </c>
       <c r="B106" s="13" t="n">
-        <v>46800</v>
+        <v>68218</v>
       </c>
     </row>
     <row r="107">
@@ -4064,7 +4050,7 @@
         </is>
       </c>
       <c r="B112" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
     </row>
     <row r="113">
@@ -4103,7 +4089,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Ties to the October 2025 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the October 2025 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4124,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>2200</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="123">
@@ -4219,7 +4205,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4231,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>1800</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="136">
@@ -4255,7 +4241,7 @@
         </is>
       </c>
       <c r="B136" s="13" t="n">
-        <v>-40</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="137">
@@ -4275,7 +4261,7 @@
         </is>
       </c>
       <c r="B138" s="17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139">
@@ -4326,7 +4312,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4348,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="150">
@@ -4382,7 +4368,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152">
@@ -4433,7 +4419,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4445,7 @@
         </is>
       </c>
       <c r="B161" s="13" t="n">
-        <v>3400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="162">
@@ -4469,7 +4455,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-70</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="163">
@@ -4489,7 +4475,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165">
@@ -4540,7 +4526,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4552,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>3200</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="175">
@@ -4576,7 +4562,7 @@
         </is>
       </c>
       <c r="B175" s="13" t="n">
-        <v>-60</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="176">
@@ -4596,7 +4582,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178">
@@ -4647,7 +4633,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4659,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="188">
@@ -4683,7 +4669,7 @@
         </is>
       </c>
       <c r="B188" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="189">
@@ -4703,7 +4689,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="191">
@@ -4780,7 +4766,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>4100</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="201">
@@ -4861,7 +4847,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4873,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>4200</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="214">
@@ -4897,7 +4883,7 @@
         </is>
       </c>
       <c r="B214" s="13" t="n">
-        <v>-90</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="215">
@@ -4917,7 +4903,7 @@
         </is>
       </c>
       <c r="B216" s="17" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="217">
@@ -4968,7 +4954,7 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4980,7 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>2800</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="227">
@@ -5004,7 +4990,7 @@
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>-60</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="228">
@@ -5024,7 +5010,7 @@
         </is>
       </c>
       <c r="B229" s="17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="230">
@@ -5101,7 +5087,7 @@
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>2600</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="240">
@@ -5208,7 +5194,7 @@
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>3900</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="253">
@@ -5315,7 +5301,7 @@
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>2400</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="266">
@@ -5427,10 +5413,10 @@
         </is>
       </c>
       <c r="B278" s="13" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="C278" s="13" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
     </row>
     <row r="279">
@@ -5512,10 +5498,10 @@
         </is>
       </c>
       <c r="B287" s="13" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="C287" s="13" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
     </row>
     <row r="288">
@@ -5592,7 +5578,7 @@
         </is>
       </c>
       <c r="B296" s="13" t="n">
-        <v>49446</v>
+        <v>64114</v>
       </c>
     </row>
     <row r="297">
@@ -5602,7 +5588,7 @@
         </is>
       </c>
       <c r="B297" s="13" t="n">
-        <v>46800</v>
+        <v>68218</v>
       </c>
     </row>
     <row r="298">
@@ -5665,7 +5651,7 @@
         </is>
       </c>
       <c r="B303" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
     </row>
     <row r="304">
@@ -5704,7 +5690,7 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>Ties to the October 2025 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the October 2025 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5725,7 @@
         </is>
       </c>
       <c r="B313" s="13" t="n">
-        <v>16800</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="314">
@@ -5846,7 +5832,7 @@
         </is>
       </c>
       <c r="B326" s="13" t="n">
-        <v>18500</v>
+        <v>20700</v>
       </c>
     </row>
     <row r="327">
@@ -5953,7 +5939,7 @@
         </is>
       </c>
       <c r="B339" s="13" t="n">
-        <v>35500</v>
+        <v>39800</v>
       </c>
     </row>
     <row r="340">
@@ -6065,10 +6051,10 @@
         </is>
       </c>
       <c r="B352" s="13" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="C352" s="13" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
     </row>
     <row r="353">
@@ -6150,10 +6136,10 @@
         </is>
       </c>
       <c r="B361" s="13" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="C361" s="13" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
     </row>
     <row r="362">
@@ -6230,7 +6216,7 @@
         </is>
       </c>
       <c r="B370" s="13" t="n">
-        <v>49446</v>
+        <v>64114</v>
       </c>
     </row>
     <row r="371">
@@ -6240,7 +6226,7 @@
         </is>
       </c>
       <c r="B371" s="13" t="n">
-        <v>46800</v>
+        <v>68218</v>
       </c>
     </row>
     <row r="372">
@@ -6303,7 +6289,7 @@
         </is>
       </c>
       <c r="B377" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
     </row>
     <row r="378">
@@ -6342,7 +6328,7 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>Ties to the October 2025 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the October 2025 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6344,7 @@
     <row r="385">
       <c r="A385" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -6373,11 +6359,11 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B387" s="13" t="n">
-        <v>15005</v>
+        <v>16873</v>
       </c>
     </row>
     <row r="388">
@@ -6455,7 +6441,7 @@
     <row r="397">
       <c r="A397" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -6470,11 +6456,11 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B399" s="13" t="n">
-        <v>15005</v>
+        <v>16873</v>
       </c>
     </row>
     <row r="400">
@@ -6577,11 +6563,11 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B412" s="13" t="n">
-        <v>1015</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="413">
@@ -6684,11 +6670,11 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B425" s="13" t="n">
-        <v>651</v>
+        <v>735</v>
       </c>
     </row>
     <row r="426">
@@ -6791,11 +6777,11 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B438" s="13" t="n">
-        <v>2610</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="439">
@@ -6898,11 +6884,11 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B451" s="13" t="n">
-        <v>2899</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="452">
@@ -7005,11 +6991,11 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B464" s="13" t="n">
-        <v>4350</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="465">
@@ -7112,11 +7098,11 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B477" s="13" t="n">
-        <v>3480</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="478">
@@ -7191,7 +7177,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7264,13 +7250,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Report: Job gross margin by type of job, October 2025: Break-even 52.5%</t>
+          <t>Report: Job gross margin by type of job, October 2025: Break-even 62.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>0.525</v>
+        <v>0.62</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7278,7 +7264,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>0.525</v>
+        <v>0.62</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -7312,13 +7298,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each maintenance contract, October 2025: Break-even 52.5%</t>
+          <t>Report: Job gross margin on each maintenance contract, October 2025: Break-even 62.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>0.525</v>
+        <v>0.62</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -7326,7 +7312,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>0.525</v>
+        <v>0.62</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -7360,13 +7346,13 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each installation invoiced in October 2025: Break-even 52.5%</t>
+          <t>Report: Job gross margin on each installation invoiced in October 2025: Break-even 62.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>0.525</v>
+        <v>0.62</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -7374,7 +7360,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>0.525</v>
+        <v>0.62</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -7408,13 +7394,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on call-outs by length, October 2025: Break-even 52.5%</t>
+          <t>Report: Job gross margin on call-outs by length, October 2025: Break-even 62.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>0.525</v>
+        <v>0.62</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -7422,7 +7408,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>0.525</v>
+        <v>0.62</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -7468,7 +7454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7513,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>171009</v>
+        <v>191014</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>114334</v>
@@ -7558,7 +7544,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>179474</v>
+        <v>200124</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>113016</v>
@@ -7589,7 +7575,7 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>143156</v>
+        <v>159406</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>85316</v>
@@ -7620,7 +7606,7 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>140909</v>
+        <v>156794</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>80742</v>
@@ -7651,7 +7637,7 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>160943</v>
+        <v>179190</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>102348</v>
@@ -7682,7 +7668,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>135082</v>
+        <v>150465</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>85752</v>
@@ -7713,7 +7699,7 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>124705</v>
+        <v>138865</v>
       </c>
       <c r="E12" s="13" t="n">
         <v>76808</v>
@@ -7744,7 +7730,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>129816</v>
+        <v>144649</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>83700</v>
@@ -7775,7 +7761,7 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>164113</v>
+        <v>183265</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>97584</v>
@@ -7806,7 +7792,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>120326</v>
@@ -7837,7 +7823,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>78258</v>
@@ -7868,7 +7854,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>80054</v>
@@ -7899,7 +7885,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>79452</v>
@@ -7930,7 +7916,7 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>10420</v>
@@ -7961,7 +7947,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>10420</v>
@@ -7992,7 +7978,7 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>10420</v>
@@ -8023,7 +8009,7 @@
         </is>
       </c>
       <c r="D22" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>10420</v>
@@ -8054,7 +8040,7 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>11782</v>
@@ -8085,7 +8071,7 @@
         </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>11782</v>
@@ -8116,7 +8102,7 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>11782</v>
@@ -8147,7 +8133,7 @@
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>11782</v>
@@ -8178,7 +8164,7 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>31870</v>
+        <v>35720</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>13446</v>
@@ -8209,7 +8195,7 @@
         </is>
       </c>
       <c r="D28" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>13446</v>
@@ -8240,7 +8226,7 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>13446</v>
@@ -8271,7 +8257,7 @@
         </is>
       </c>
       <c r="D30" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>13446</v>
@@ -8302,7 +8288,7 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>14516</v>
@@ -8333,7 +8319,7 @@
         </is>
       </c>
       <c r="D32" s="13" t="n">
-        <v>126300</v>
+        <v>141600</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>92430</v>
@@ -8364,7 +8350,7 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>131400</v>
+        <v>147100</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>89070</v>
@@ -8395,7 +8381,7 @@
         </is>
       </c>
       <c r="D34" s="13" t="n">
-        <v>92600</v>
+        <v>103700</v>
       </c>
       <c r="E34" s="13" t="n">
         <v>59908</v>
@@ -8426,7 +8412,7 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>89400</v>
+        <v>100100</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>54678</v>
@@ -8457,7 +8443,7 @@
         </is>
       </c>
       <c r="D36" s="13" t="n">
-        <v>106000</v>
+        <v>118600</v>
       </c>
       <c r="E36" s="13" t="n">
         <v>74966</v>
@@ -8488,7 +8474,7 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>86100</v>
+        <v>96400</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>61664</v>
@@ -8519,7 +8505,7 @@
         </is>
       </c>
       <c r="D38" s="13" t="n">
-        <v>74900</v>
+        <v>83900</v>
       </c>
       <c r="E38" s="13" t="n">
         <v>52264</v>
@@ -8550,7 +8536,7 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>80300</v>
+        <v>89900</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>59534</v>
@@ -8581,7 +8567,7 @@
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>112700</v>
+        <v>126300</v>
       </c>
       <c r="E40" s="13" t="n">
         <v>72976</v>
@@ -8612,7 +8598,7 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>96920</v>
@@ -8643,7 +8629,7 @@
         </is>
       </c>
       <c r="D42" s="13" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
       <c r="E42" s="13" t="n">
         <v>53590</v>
@@ -8674,7 +8660,7 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
       <c r="E43" s="13" t="n">
         <v>55440</v>
@@ -8705,7 +8691,7 @@
         </is>
       </c>
       <c r="D44" s="13" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="E44" s="13" t="n">
         <v>52288</v>
@@ -8736,7 +8722,7 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>20039</v>
+        <v>21764</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>11484</v>
@@ -8767,7 +8753,7 @@
         </is>
       </c>
       <c r="D46" s="13" t="n">
-        <v>23404</v>
+        <v>25374</v>
       </c>
       <c r="E46" s="13" t="n">
         <v>13526</v>
@@ -8798,7 +8784,7 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>25886</v>
+        <v>28056</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>14988</v>
@@ -8829,7 +8815,7 @@
         </is>
       </c>
       <c r="D48" s="13" t="n">
-        <v>26839</v>
+        <v>29044</v>
       </c>
       <c r="E48" s="13" t="n">
         <v>15644</v>
@@ -8860,7 +8846,7 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>27013</v>
+        <v>29290</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>15600</v>
@@ -8891,7 +8877,7 @@
         </is>
       </c>
       <c r="D50" s="13" t="n">
-        <v>21052</v>
+        <v>22765</v>
       </c>
       <c r="E50" s="13" t="n">
         <v>12306</v>
@@ -8922,7 +8908,7 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>21875</v>
+        <v>23665</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>12762</v>
@@ -8953,7 +8939,7 @@
         </is>
       </c>
       <c r="D52" s="13" t="n">
-        <v>21586</v>
+        <v>23449</v>
       </c>
       <c r="E52" s="13" t="n">
         <v>12384</v>
@@ -8984,7 +8970,7 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>19543</v>
+        <v>21245</v>
       </c>
       <c r="E53" s="13" t="n">
         <v>11162</v>
@@ -9015,7 +9001,7 @@
         </is>
       </c>
       <c r="D54" s="13" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="E54" s="13" t="n">
         <v>9960</v>
@@ -9046,7 +9032,7 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>11222</v>
@@ -9077,7 +9063,7 @@
         </is>
       </c>
       <c r="D56" s="13" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
       <c r="E56" s="13" t="n">
         <v>11168</v>
@@ -9108,7 +9094,7 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>12648</v>
@@ -9128,7 +9114,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2025-10/job-margins.xlsx
+++ b/media/exports/reports/2025-10/job-margins.xlsx
@@ -13,21 +13,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Job_gross_margin_October_All_jobs">'Report'!$B$15</definedName>
-    <definedName name="Job_gross_margin_September_All_jobs">'Report'!$B$16</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$17</definedName>
-    <definedName name="Job_gross_margin_October_Maintenance_contracts">'Report'!$B$41</definedName>
-    <definedName name="Job_gross_margin_September_Maintenance_contracts">'Report'!$B$42</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$43</definedName>
-    <definedName name="Job_gross_margin_October_Installations">'Report'!$B$77</definedName>
-    <definedName name="Job_gross_margin_September_Installations">'Report'!$B$78</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$79</definedName>
-    <definedName name="Job_gross_margin_October_Call_outs_and_repairs">'Report'!$B$103</definedName>
-    <definedName name="Job_gross_margin_September_Call_outs_and_repairs">'Report'!$B$104</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$105</definedName>
-    <definedName name="Technician_time_charged_October">'Report'!$B$106</definedName>
-    <definedName name="Materials_charged_October">'Report'!$B$107</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$132</definedName>
+    <definedName name="Job_gross_margin_October_All_jobs">'Report'!$B$16</definedName>
+    <definedName name="Job_gross_margin_September_All_jobs">'Report'!$B$17</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$18</definedName>
+    <definedName name="Job_gross_margin_October_Maintenance_contracts">'Report'!$B$42</definedName>
+    <definedName name="Job_gross_margin_September_Maintenance_contracts">'Report'!$B$43</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$44</definedName>
+    <definedName name="Job_gross_margin_October_Installations">'Report'!$B$78</definedName>
+    <definedName name="Job_gross_margin_September_Installations">'Report'!$B$79</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$80</definedName>
+    <definedName name="Job_gross_margin_October_Call_outs_and_repairs">'Report'!$B$104</definedName>
+    <definedName name="Job_gross_margin_September_Call_outs_and_repairs">'Report'!$B$105</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$106</definedName>
+    <definedName name="Technician_time_charged_October">'Report'!$B$107</definedName>
+    <definedName name="Materials_charged_October">'Report'!$B$108</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$133</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$483</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$57</definedName>
@@ -67,6 +67,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
@@ -92,11 +97,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
   </fonts>
   <fills count="3">
@@ -129,36 +129,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -319,12 +322,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$21:$A$23</f>
+              <f>'Report'!$A$22:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$21:$B$23</f>
+              <f>'Report'!$B$22:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -603,12 +606,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$47:$A$58</f>
+              <f>'Report'!$A$48:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$47:$B$58</f>
+              <f>'Report'!$B$48:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -901,12 +904,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$83:$A$85</f>
+              <f>'Report'!$A$84:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$83:$B$85</f>
+              <f>'Report'!$B$84:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -1185,12 +1188,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$111:$A$116</f>
+              <f>'Report'!$A$112:$A$117</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$111:$B$116</f>
+              <f>'Report'!$B$112:$B$117</f>
             </numRef>
           </val>
         </ser>
@@ -1619,7 +1622,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2196000"/>
@@ -1641,7 +1644,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="4176000"/>
@@ -1663,7 +1666,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2196000"/>
@@ -1685,7 +1688,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2556000"/>
@@ -2038,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2064,7 +2067,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2072,92 +2075,83 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Jobs made a 44.7% gross margin in October: maintenance contracts the most (63.8%), installations the least (34.1%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Pick a type of job and every number, chart and note on the page follows it.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>From gross margin to profit</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>October's jobs made $64,114 gross margin (44.7%). Technician time not charged to jobs took $31,056 and overheads $57,980, leaving ($24,922) profit before tax ((17.4%) of revenue). To cover overheads, jobs need a 62.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Gross margin, not profit</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: All jobs</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>Type of job: All jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Job gross margin, October · All jobs</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>Workings!B28</f>
-        <v/>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Job gross margin, September · All jobs</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+          <t>Job gross margin, October · All jobs</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>Workings!B28</f>
+        <v/>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2166,86 +2160,101 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Job gross margin, September · All jobs</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>Workings!C37</f>
+        <v/>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B18" s="9">
         <f>Workings!B53</f>
         <v/>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (October)</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Job gross margin by type of job, October 2025</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B21" s="8">
-        <f>Workings!B63</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>Workings!B62</f>
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Installations</t>
-        </is>
-      </c>
-      <c r="B22" s="8">
-        <f>Workings!B72</f>
-        <v/>
-      </c>
-      <c r="C22" s="11">
-        <f>Workings!B71</f>
+          <t>Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>Workings!B63</f>
+        <v/>
+      </c>
+      <c r="C22" s="12">
+        <f>Workings!B62</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Installations</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+      <c r="C23" s="12">
+        <f>Workings!B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B24" s="9">
         <f>Workings!B81</f>
         <v/>
       </c>
-      <c r="C23" s="11">
+      <c r="C24" s="12">
         <f>Workings!B80</f>
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
@@ -2254,87 +2263,72 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>In October maintenance contracts made a 63.8% job gross margin, installations made a 34.1% job gross margin, call-outs and repairs made a 47.7% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 62.0% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Installations: 34.1% gross margin, 0.9 points under the 35.0% target: about $743 on $79,300 of revenue in October. It's below the 62.0% needed to cover overheads, too. Maintenance contracts: 63.8% gross margin, 28.8 points over the 35.0% target ($11,549 ahead on $40,100 in October).</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Maintenance contracts</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Maintenance contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Job gross margin, October · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B41" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Job gross margin, September · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B42" s="8">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
+          <t>Job gross margin, October · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B42" s="9">
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2343,221 +2337,236 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Job gross margin, September · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B43" s="9">
+        <f>Workings!C99</f>
+        <v/>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B43" s="8">
+      <c r="B44" s="9">
         <f>Workings!B115</f>
         <v/>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (October)</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on each maintenance contract, October 2025</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr"/>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B47" s="8">
-        <f>Workings!B129</f>
-        <v/>
-      </c>
-      <c r="C47" s="11">
-        <f>Workings!B128</f>
-        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
-        </is>
-      </c>
-      <c r="B48" s="8">
-        <f>Workings!B142</f>
-        <v/>
-      </c>
-      <c r="C48" s="11">
-        <f>Workings!B141</f>
+          <t>Wynnum medical centre</t>
+        </is>
+      </c>
+      <c r="B48" s="9">
+        <f>Workings!B129</f>
+        <v/>
+      </c>
+      <c r="C48" s="12">
+        <f>Workings!B128</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
-        </is>
-      </c>
-      <c r="B49" s="8">
-        <f>Workings!B155</f>
-        <v/>
-      </c>
-      <c r="C49" s="11">
-        <f>Workings!B154</f>
+          <t>Ashgrove aged care</t>
+        </is>
+      </c>
+      <c r="B49" s="9">
+        <f>Workings!B142</f>
+        <v/>
+      </c>
+      <c r="C49" s="12">
+        <f>Workings!B141</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
-        </is>
-      </c>
-      <c r="B50" s="8">
-        <f>Workings!B168</f>
-        <v/>
-      </c>
-      <c r="C50" s="11">
-        <f>Workings!B167</f>
+          <t>Riverside Apartments (strata)</t>
+        </is>
+      </c>
+      <c r="B50" s="9">
+        <f>Workings!B155</f>
+        <v/>
+      </c>
+      <c r="C50" s="12">
+        <f>Workings!B154</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
-        </is>
-      </c>
-      <c r="B51" s="8">
-        <f>Workings!B181</f>
-        <v/>
-      </c>
-      <c r="C51" s="11">
-        <f>Workings!B180</f>
+          <t>Newstead gym</t>
+        </is>
+      </c>
+      <c r="B51" s="9">
+        <f>Workings!B168</f>
+        <v/>
+      </c>
+      <c r="C51" s="12">
+        <f>Workings!B167</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B52" s="8">
-        <f>Workings!B194</f>
-        <v/>
-      </c>
-      <c r="C52" s="11">
-        <f>Workings!B193</f>
+          <t>Fortitude Valley hotel</t>
+        </is>
+      </c>
+      <c r="B52" s="9">
+        <f>Workings!B181</f>
+        <v/>
+      </c>
+      <c r="C52" s="12">
+        <f>Workings!B180</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
-        </is>
-      </c>
-      <c r="B53" s="8">
-        <f>Workings!B207</f>
-        <v/>
-      </c>
-      <c r="C53" s="11">
-        <f>Workings!B206</f>
+          <t>Southbank cafe group</t>
+        </is>
+      </c>
+      <c r="B53" s="9">
+        <f>Workings!B194</f>
+        <v/>
+      </c>
+      <c r="C53" s="12">
+        <f>Workings!B193</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
-        </is>
-      </c>
-      <c r="B54" s="8">
-        <f>Workings!B220</f>
-        <v/>
-      </c>
-      <c r="C54" s="11">
-        <f>Workings!B219</f>
+          <t>Chermside retail centre</t>
+        </is>
+      </c>
+      <c r="B54" s="9">
+        <f>Workings!B207</f>
+        <v/>
+      </c>
+      <c r="C54" s="12">
+        <f>Workings!B206</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
-        </is>
-      </c>
-      <c r="B55" s="8">
-        <f>Workings!B233</f>
-        <v/>
-      </c>
-      <c r="C55" s="11">
-        <f>Workings!B232</f>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B55" s="9">
+        <f>Workings!B220</f>
+        <v/>
+      </c>
+      <c r="C55" s="12">
+        <f>Workings!B219</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>West End brewery</t>
-        </is>
-      </c>
-      <c r="B56" s="8">
-        <f>Workings!B246</f>
-        <v/>
-      </c>
-      <c r="C56" s="11">
-        <f>Workings!B245</f>
+          <t>Milton office tower</t>
+        </is>
+      </c>
+      <c r="B56" s="9">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C56" s="12">
+        <f>Workings!B232</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
-        </is>
-      </c>
-      <c r="B57" s="8">
-        <f>Workings!B259</f>
-        <v/>
-      </c>
-      <c r="C57" s="11">
-        <f>Workings!B258</f>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B57" s="9">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C57" s="12">
+        <f>Workings!B245</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B58" s="9">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C58" s="12">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B58" s="8">
+      <c r="B59" s="9">
         <f>Workings!B272</f>
         <v/>
       </c>
-      <c r="C58" s="11">
+      <c r="C59" s="12">
         <f>Workings!B271</f>
         <v/>
       </c>
     </row>
-    <row r="59"/>
     <row r="60"/>
     <row r="61"/>
     <row r="62"/>
@@ -2567,87 +2576,72 @@
     <row r="66"/>
     <row r="67"/>
     <row r="68"/>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 62.9% job gross margin: 14.0 h of technician time on a $2,700 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>The thinnest, Kangaroo Point townhouses: 62.9% gross margin, 27.9 points over the 35.0% target ($753 ahead on $2,700 in October). All maintenance contracts: 63.8% gross margin, 28.8 points over the 35.0% target ($11,549 ahead on $40,100 in October).</t>
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Installations</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Job gross margin, October · Installations</t>
-        </is>
-      </c>
-      <c r="B77" s="8">
-        <f>Workings!B281</f>
-        <v/>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Job gross margin, September · Installations</t>
-        </is>
-      </c>
-      <c r="B78" s="8">
-        <f>Workings!B290</f>
-        <v/>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
+          <t>Job gross margin, October · Installations</t>
+        </is>
+      </c>
+      <c r="B78" s="9">
+        <f>Workings!B281</f>
+        <v/>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2656,86 +2650,101 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Job gross margin, September · Installations</t>
+        </is>
+      </c>
+      <c r="B79" s="9">
+        <f>Workings!C290</f>
+        <v/>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B79" s="8">
+      <c r="B80" s="9">
         <f>Workings!B306</f>
         <v/>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (October)</t>
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on each installation invoiced in October 2025</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr"/>
-      <c r="B82" s="7" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr"/>
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Aspley cafe data cabling</t>
-        </is>
-      </c>
-      <c r="B83" s="8">
-        <f>Workings!B320</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>Workings!B319</f>
-        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Coorparoo shop air-con install</t>
-        </is>
-      </c>
-      <c r="B84" s="8">
-        <f>Workings!B333</f>
-        <v/>
-      </c>
-      <c r="C84" s="11">
-        <f>Workings!B332</f>
+          <t>Aspley cafe data cabling</t>
+        </is>
+      </c>
+      <c r="B84" s="9">
+        <f>Workings!B320</f>
+        <v/>
+      </c>
+      <c r="C84" s="12">
+        <f>Workings!B319</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Coorparoo shop air-con install</t>
+        </is>
+      </c>
+      <c r="B85" s="9">
+        <f>Workings!B333</f>
+        <v/>
+      </c>
+      <c r="C85" s="12">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>Salisbury shop solar and battery</t>
         </is>
       </c>
-      <c r="B85" s="8">
+      <c r="B86" s="9">
         <f>Workings!B346</f>
         <v/>
       </c>
-      <c r="C85" s="11">
+      <c r="C86" s="12">
         <f>Workings!B345</f>
         <v/>
       </c>
     </row>
-    <row r="86"/>
     <row r="87"/>
     <row r="88"/>
     <row r="89"/>
@@ -2744,87 +2753,72 @@
     <row r="92"/>
     <row r="93"/>
     <row r="94"/>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>1 of the 3 installation jobs invoiced in October made less than the 35.0% job gross margin target. The Salisbury shop solar and battery made a 26.2% job gross margin: 120.0 h of technician time ($8,160) and $3,900 of subcontractors on a $39,800 job. Jobs need 62.0% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="97"/>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>1 installation under the 35.0% target, worth about $3,490 between them on $39,800 of revenue. The biggest gap, Salisbury shop solar and battery: 26.2% gross margin, 8.8 points under the 35.0% target: about $3,490 on $39,800 of revenue in October. It's below the 62.0% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Call-outs and repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Job gross margin, October · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B103" s="8">
-        <f>Workings!B355</f>
-        <v/>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Job gross margin, September · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B104" s="8">
-        <f>Workings!B364</f>
-        <v/>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
+          <t>Job gross margin, October · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B104" s="9">
+        <f>Workings!B355</f>
+        <v/>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2833,163 +2827,178 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B105" s="8">
-        <f>Workings!B380</f>
-        <v/>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (October)</t>
+          <t>Job gross margin, September · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B105" s="9">
+        <f>Workings!C364</f>
+        <v/>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Technician time charged, October</t>
-        </is>
-      </c>
-      <c r="B106" s="8">
-        <f>Workings!B393</f>
-        <v/>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>69.8% of call-out revenue</t>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B106" s="9">
+        <f>Workings!B380</f>
+        <v/>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (October)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>Technician time charged, October</t>
+        </is>
+      </c>
+      <c r="B107" s="12">
+        <f>Workings!B387</f>
+        <v/>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>69.8% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>Materials charged, October</t>
         </is>
       </c>
-      <c r="B107" s="8">
-        <f>Workings!B405</f>
-        <v/>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="B108" s="12">
+        <f>Workings!B403</f>
+        <v/>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>$5,610 at cost, plus 30%</t>
         </is>
       </c>
     </row>
-    <row r="108"/>
-    <row r="109">
-      <c r="A109" s="10" t="inlineStr">
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, October 2025</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr"/>
-      <c r="B110" s="7" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr"/>
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C110" s="7" t="inlineStr">
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (7)</t>
-        </is>
-      </c>
-      <c r="B111" s="8">
-        <f>Workings!B418</f>
-        <v/>
-      </c>
-      <c r="C111" s="11">
-        <f>Workings!B417</f>
-        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1.5-hour call-outs (3)</t>
-        </is>
-      </c>
-      <c r="B112" s="8">
-        <f>Workings!B431</f>
-        <v/>
-      </c>
-      <c r="C112" s="11">
-        <f>Workings!B430</f>
+          <t>1-hour call-outs (7)</t>
+        </is>
+      </c>
+      <c r="B112" s="9">
+        <f>Workings!B418</f>
+        <v/>
+      </c>
+      <c r="C112" s="12">
+        <f>Workings!B417</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2-hour call-outs (9)</t>
-        </is>
-      </c>
-      <c r="B113" s="8">
-        <f>Workings!B444</f>
-        <v/>
-      </c>
-      <c r="C113" s="11">
-        <f>Workings!B443</f>
+          <t>1.5-hour call-outs (3)</t>
+        </is>
+      </c>
+      <c r="B113" s="9">
+        <f>Workings!B431</f>
+        <v/>
+      </c>
+      <c r="C113" s="12">
+        <f>Workings!B430</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (8)</t>
-        </is>
-      </c>
-      <c r="B114" s="8">
-        <f>Workings!B457</f>
-        <v/>
-      </c>
-      <c r="C114" s="11">
-        <f>Workings!B456</f>
+          <t>2-hour call-outs (9)</t>
+        </is>
+      </c>
+      <c r="B114" s="9">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C114" s="12">
+        <f>Workings!B443</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3-hour call-outs (10)</t>
-        </is>
-      </c>
-      <c r="B115" s="8">
-        <f>Workings!B470</f>
-        <v/>
-      </c>
-      <c r="C115" s="11">
-        <f>Workings!B469</f>
+          <t>2.5-hour call-outs (8)</t>
+        </is>
+      </c>
+      <c r="B115" s="9">
+        <f>Workings!B457</f>
+        <v/>
+      </c>
+      <c r="C115" s="12">
+        <f>Workings!B456</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>3-hour call-outs (10)</t>
+        </is>
+      </c>
+      <c r="B116" s="9">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C116" s="12">
+        <f>Workings!B469</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B116" s="8">
+      <c r="B117" s="9">
         <f>Workings!B483</f>
         <v/>
       </c>
-      <c r="C116" s="11">
+      <c r="C117" s="12">
         <f>Workings!B482</f>
         <v/>
       </c>
     </row>
-    <row r="117"/>
     <row r="118"/>
     <row r="119"/>
     <row r="120"/>
@@ -2997,83 +3006,85 @@
     <row r="122"/>
     <row r="123"/>
     <row r="124"/>
-    <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+    <row r="125"/>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" s="3" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>43 call-outs in October billed $16,873 of technician time and $7,293 of materials ($5,610 at cost plus 30%), and made a 47.7% job gross margin between them. Gross margins run from 41.4% to 50.5% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+    <row r="128"/>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="30" customHeight="1">
-      <c r="A129" s="3" t="inlineStr">
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>All call-outs: 47.7% gross margin, 12.7 points over the 35.0% target ($3,060 ahead on $24,166 in October).</t>
         </is>
       </c>
     </row>
-    <row r="130"/>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="131"/>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="12" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="13" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="133"/>
     <row r="134"/>
+    <row r="135"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A127:D127"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A71:D71"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="5" manualBreakCount="5">
-    <brk id="18" min="0" max="16383" man="1"/>
-    <brk id="44" min="0" max="16383" man="1"/>
-    <brk id="68" min="0" max="16383" man="1"/>
-    <brk id="94" min="0" max="16383" man="1"/>
-    <brk id="108" min="0" max="16383" man="1"/>
+    <brk id="19" min="0" max="16383" man="1"/>
+    <brk id="45" min="0" max="16383" man="1"/>
+    <brk id="69" min="0" max="16383" man="1"/>
+    <brk id="95" min="0" max="16383" man="1"/>
+    <brk id="109" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -3111,28 +3122,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -3144,7 +3155,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>64114</v>
       </c>
     </row>
@@ -3154,7 +3165,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>68218</v>
       </c>
     </row>
@@ -3164,7 +3175,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>37162</v>
       </c>
     </row>
@@ -3174,7 +3185,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="14">
         <f>B9-B10</f>
         <v/>
       </c>
@@ -3185,7 +3196,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <f>B8-B11</f>
         <v/>
       </c>
@@ -3196,7 +3207,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>57980</v>
       </c>
     </row>
@@ -3206,7 +3217,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <f>B12-B13</f>
         <v/>
       </c>
@@ -3217,7 +3228,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>143566</v>
       </c>
     </row>
@@ -3227,7 +3238,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <f>B8/B15</f>
         <v/>
       </c>
@@ -3238,18 +3249,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="15">
         <f>B14/B15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="17">
         <f>(B11+B13)/B15</f>
         <v/>
       </c>
@@ -3264,27 +3275,27 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Trades, all lines: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr"/>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
@@ -3296,10 +3307,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>143566</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="14" t="n">
         <v>143077</v>
       </c>
     </row>
@@ -3309,10 +3320,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="14" t="n">
         <v>79452</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="14" t="n">
         <v>80054</v>
       </c>
     </row>
@@ -3322,26 +3333,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <f>B25-B26</f>
         <v/>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="14">
         <f>C25-C26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <f>B27/B25</f>
         <v/>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="17">
         <f>C27/C25</f>
         <v/>
       </c>
@@ -3349,27 +3360,27 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Trades, all lines: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
@@ -3381,10 +3392,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n">
+      <c r="B34" s="14" t="n">
         <v>143566</v>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C34" s="14" t="n">
         <v>143077</v>
       </c>
     </row>
@@ -3394,10 +3405,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="14" t="n">
         <v>79452</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="14" t="n">
         <v>80054</v>
       </c>
     </row>
@@ -3407,26 +3418,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <f>B34-B35</f>
         <v/>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="14">
         <f>C34-C35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <f>B36/B34</f>
         <v/>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="17">
         <f>C36/C34</f>
         <v/>
       </c>
@@ -3434,22 +3445,22 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -3461,7 +3472,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="14" t="n">
         <v>64114</v>
       </c>
     </row>
@@ -3471,7 +3482,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="14" t="n">
         <v>68218</v>
       </c>
     </row>
@@ -3481,7 +3492,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n">
+      <c r="B45" s="14" t="n">
         <v>37162</v>
       </c>
     </row>
@@ -3491,7 +3502,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="14">
         <f>B44-B45</f>
         <v/>
       </c>
@@ -3502,7 +3513,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="14">
         <f>B43-B46</f>
         <v/>
       </c>
@@ -3513,7 +3524,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
+      <c r="B48" s="14" t="n">
         <v>57980</v>
       </c>
     </row>
@@ -3523,7 +3534,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <f>B47-B48</f>
         <v/>
       </c>
@@ -3534,7 +3545,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B50" s="13" t="n">
+      <c r="B50" s="14" t="n">
         <v>143566</v>
       </c>
     </row>
@@ -3544,7 +3555,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="15">
         <f>B43/B50</f>
         <v/>
       </c>
@@ -3555,18 +3566,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="15">
         <f>B49/B50</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="17">
         <f>(B46+B48)/B50</f>
         <v/>
       </c>
@@ -3581,22 +3592,22 @@
     <row r="55"/>
     <row r="56"/>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Maintenance contracts, October</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr"/>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -3608,7 +3619,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B60" s="13" t="n">
+      <c r="B60" s="14" t="n">
         <v>40100</v>
       </c>
     </row>
@@ -3618,7 +3629,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B61" s="13" t="n">
+      <c r="B61" s="14" t="n">
         <v>14516</v>
       </c>
     </row>
@@ -3628,18 +3639,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <f>B60-B61</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="17">
         <f>B62/B60</f>
         <v/>
       </c>
@@ -3647,22 +3658,22 @@
     <row r="64"/>
     <row r="65"/>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Installations, October</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr"/>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr"/>
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -3674,7 +3685,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B69" s="13" t="n">
+      <c r="B69" s="14" t="n">
         <v>79300</v>
       </c>
     </row>
@@ -3684,7 +3695,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B70" s="13" t="n">
+      <c r="B70" s="14" t="n">
         <v>52288</v>
       </c>
     </row>
@@ -3694,18 +3705,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="14">
         <f>B69-B70</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="inlineStr">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="17">
         <f>B71/B69</f>
         <v/>
       </c>
@@ -3713,22 +3724,22 @@
     <row r="73"/>
     <row r="74"/>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>Call-outs and repairs, October</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr"/>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr"/>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -3740,7 +3751,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B78" s="13" t="n">
+      <c r="B78" s="14" t="n">
         <v>24166</v>
       </c>
     </row>
@@ -3750,7 +3761,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B79" s="13" t="n">
+      <c r="B79" s="14" t="n">
         <v>12648</v>
       </c>
     </row>
@@ -3760,18 +3771,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="14">
         <f>B78-B79</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
+      <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="17">
         <f>B80/B78</f>
         <v/>
       </c>
@@ -3779,27 +3790,27 @@
     <row r="82"/>
     <row r="83"/>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Trades, Maintenance contracts: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr"/>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr"/>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
@@ -3811,10 +3822,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B87" s="13" t="n">
+      <c r="B87" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="C87" s="13" t="n">
+      <c r="C87" s="14" t="n">
         <v>37200</v>
       </c>
     </row>
@@ -3824,10 +3835,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B88" s="13" t="n">
+      <c r="B88" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="C88" s="13" t="n">
+      <c r="C88" s="14" t="n">
         <v>13446</v>
       </c>
     </row>
@@ -3837,26 +3848,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B89" s="13">
+      <c r="B89" s="14">
         <f>B87-B88</f>
         <v/>
       </c>
-      <c r="C89" s="13">
+      <c r="C89" s="14">
         <f>C87-C88</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="inlineStr">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B90" s="16">
+      <c r="B90" s="17">
         <f>B89/B87</f>
         <v/>
       </c>
-      <c r="C90" s="16">
+      <c r="C90" s="17">
         <f>C89/C87</f>
         <v/>
       </c>
@@ -3864,27 +3875,27 @@
     <row r="91"/>
     <row r="92"/>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>Trades, Maintenance contracts: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+      <c r="A94" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="inlineStr"/>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr"/>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
@@ -3896,10 +3907,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B96" s="13" t="n">
+      <c r="B96" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="C96" s="13" t="n">
+      <c r="C96" s="14" t="n">
         <v>37200</v>
       </c>
     </row>
@@ -3909,10 +3920,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B97" s="13" t="n">
+      <c r="B97" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="C97" s="13" t="n">
+      <c r="C97" s="14" t="n">
         <v>13446</v>
       </c>
     </row>
@@ -3922,26 +3933,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B98" s="13">
+      <c r="B98" s="14">
         <f>B96-B97</f>
         <v/>
       </c>
-      <c r="C98" s="13">
+      <c r="C98" s="14">
         <f>C96-C97</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B99" s="16">
+      <c r="B99" s="17">
         <f>B98/B96</f>
         <v/>
       </c>
-      <c r="C99" s="16">
+      <c r="C99" s="17">
         <f>C98/C96</f>
         <v/>
       </c>
@@ -3949,22 +3960,22 @@
     <row r="100"/>
     <row r="101"/>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+      <c r="A103" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="inlineStr"/>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr"/>
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -3976,7 +3987,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B105" s="13" t="n">
+      <c r="B105" s="14" t="n">
         <v>64114</v>
       </c>
     </row>
@@ -3986,7 +3997,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B106" s="13" t="n">
+      <c r="B106" s="14" t="n">
         <v>68218</v>
       </c>
     </row>
@@ -3996,7 +4007,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B107" s="13" t="n">
+      <c r="B107" s="14" t="n">
         <v>37162</v>
       </c>
     </row>
@@ -4006,7 +4017,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B108" s="13">
+      <c r="B108" s="14">
         <f>B106-B107</f>
         <v/>
       </c>
@@ -4017,7 +4028,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B109" s="13">
+      <c r="B109" s="14">
         <f>B105-B108</f>
         <v/>
       </c>
@@ -4028,7 +4039,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B110" s="13" t="n">
+      <c r="B110" s="14" t="n">
         <v>57980</v>
       </c>
     </row>
@@ -4038,7 +4049,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B111" s="13">
+      <c r="B111" s="14">
         <f>B109-B110</f>
         <v/>
       </c>
@@ -4049,7 +4060,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B112" s="13" t="n">
+      <c r="B112" s="14" t="n">
         <v>143566</v>
       </c>
     </row>
@@ -4059,7 +4070,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B113" s="14">
+      <c r="B113" s="15">
         <f>B105/B112</f>
         <v/>
       </c>
@@ -4070,18 +4081,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B114" s="14">
+      <c r="B114" s="15">
         <f>B111/B112</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="15" t="inlineStr">
+      <c r="A115" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="17">
         <f>(B108+B110)/B112</f>
         <v/>
       </c>
@@ -4096,22 +4107,22 @@
     <row r="117"/>
     <row r="118"/>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>Wynnum medical centre</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="12" t="inlineStr">
+      <c r="A120" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr"/>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr"/>
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4123,7 +4134,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B122" s="13" t="n">
+      <c r="B122" s="14" t="n">
         <v>2450</v>
       </c>
     </row>
@@ -4133,7 +4144,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B123" s="13" t="n">
+      <c r="B123" s="14" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -4143,7 +4154,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B124" s="13" t="n">
+      <c r="B124" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4153,7 +4164,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B125" s="17" t="n">
+      <c r="B125" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4163,7 +4174,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B126" s="13" t="n">
+      <c r="B126" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4173,7 +4184,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B127" s="13">
+      <c r="B127" s="14">
         <f>-B125*B126</f>
         <v/>
       </c>
@@ -4184,18 +4195,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B128" s="13">
+      <c r="B128" s="14">
         <f>B122+B123+B124+B127</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="15" t="inlineStr">
+      <c r="A129" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B129" s="16">
+      <c r="B129" s="17">
         <f>B128/B122</f>
         <v/>
       </c>
@@ -4203,22 +4214,22 @@
     <row r="130"/>
     <row r="131"/>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="12" t="inlineStr">
+      <c r="A133" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr"/>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr"/>
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4230,7 +4241,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B135" s="13" t="n">
+      <c r="B135" s="14" t="n">
         <v>4050</v>
       </c>
     </row>
@@ -4240,7 +4251,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B136" s="13" t="n">
+      <c r="B136" s="14" t="n">
         <v>-80</v>
       </c>
     </row>
@@ -4250,7 +4261,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B137" s="13" t="n">
+      <c r="B137" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4260,7 +4271,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B138" s="17" t="n">
+      <c r="B138" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4270,7 +4281,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B139" s="13" t="n">
+      <c r="B139" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4280,7 +4291,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B140" s="13">
+      <c r="B140" s="14">
         <f>-B138*B139</f>
         <v/>
       </c>
@@ -4291,18 +4302,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B141" s="13">
+      <c r="B141" s="14">
         <f>B135+B136+B137+B140</f>
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="15" t="inlineStr">
+      <c r="A142" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B142" s="16">
+      <c r="B142" s="17">
         <f>B141/B135</f>
         <v/>
       </c>
@@ -4310,22 +4321,22 @@
     <row r="143"/>
     <row r="144"/>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="12" t="inlineStr">
+      <c r="A146" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="6" t="inlineStr"/>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="A147" s="7" t="inlineStr"/>
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4337,7 +4348,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B148" s="13" t="n">
+      <c r="B148" s="14" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -4347,7 +4358,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B149" s="13" t="n">
+      <c r="B149" s="14" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -4357,7 +4368,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B150" s="13" t="n">
+      <c r="B150" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4367,7 +4378,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B151" s="17" t="n">
+      <c r="B151" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4377,7 +4388,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B152" s="13" t="n">
+      <c r="B152" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4387,7 +4398,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B153" s="13">
+      <c r="B153" s="14">
         <f>-B151*B152</f>
         <v/>
       </c>
@@ -4398,18 +4409,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B154" s="13">
+      <c r="B154" s="14">
         <f>B148+B149+B150+B153</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="15" t="inlineStr">
+      <c r="A155" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B155" s="16">
+      <c r="B155" s="17">
         <f>B154/B148</f>
         <v/>
       </c>
@@ -4417,22 +4428,22 @@
     <row r="156"/>
     <row r="157"/>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>Newstead gym</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="12" t="inlineStr">
+      <c r="A159" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="inlineStr"/>
-      <c r="B160" s="7" t="inlineStr">
+      <c r="A160" s="7" t="inlineStr"/>
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4444,7 +4455,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B161" s="13" t="n">
+      <c r="B161" s="14" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -4454,7 +4465,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B162" s="13" t="n">
+      <c r="B162" s="14" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -4464,7 +4475,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B163" s="13" t="n">
+      <c r="B163" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4474,7 +4485,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B164" s="17" t="n">
+      <c r="B164" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4484,7 +4495,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B165" s="13" t="n">
+      <c r="B165" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4494,7 +4505,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B166" s="13">
+      <c r="B166" s="14">
         <f>-B164*B165</f>
         <v/>
       </c>
@@ -4505,18 +4516,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B167" s="13">
+      <c r="B167" s="14">
         <f>B161+B162+B163+B166</f>
         <v/>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="inlineStr">
+      <c r="A168" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B168" s="16">
+      <c r="B168" s="17">
         <f>B167/B161</f>
         <v/>
       </c>
@@ -4524,22 +4535,22 @@
     <row r="169"/>
     <row r="170"/>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="12" t="inlineStr">
+      <c r="A172" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr"/>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="A173" s="7" t="inlineStr"/>
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4551,7 +4562,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B174" s="13" t="n">
+      <c r="B174" s="14" t="n">
         <v>3800</v>
       </c>
     </row>
@@ -4561,7 +4572,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B175" s="13" t="n">
+      <c r="B175" s="14" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -4571,7 +4582,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B176" s="13" t="n">
+      <c r="B176" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4581,7 +4592,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B177" s="17" t="n">
+      <c r="B177" s="18" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4591,7 +4602,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B178" s="13" t="n">
+      <c r="B178" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4601,7 +4612,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B179" s="13">
+      <c r="B179" s="14">
         <f>-B177*B178</f>
         <v/>
       </c>
@@ -4612,18 +4623,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B180" s="13">
+      <c r="B180" s="14">
         <f>B174+B175+B176+B179</f>
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="15" t="inlineStr">
+      <c r="A181" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B181" s="16">
+      <c r="B181" s="17">
         <f>B180/B174</f>
         <v/>
       </c>
@@ -4631,22 +4642,22 @@
     <row r="182"/>
     <row r="183"/>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="12" t="inlineStr">
+      <c r="A185" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr"/>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="A186" s="7" t="inlineStr"/>
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4658,7 +4669,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B187" s="13" t="n">
+      <c r="B187" s="14" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -4668,7 +4679,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B188" s="13" t="n">
+      <c r="B188" s="14" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -4678,7 +4689,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B189" s="13" t="n">
+      <c r="B189" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4688,7 +4699,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B190" s="17" t="n">
+      <c r="B190" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4698,7 +4709,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B191" s="13" t="n">
+      <c r="B191" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4708,7 +4719,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B192" s="13">
+      <c r="B192" s="14">
         <f>-B190*B191</f>
         <v/>
       </c>
@@ -4719,18 +4730,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B193" s="13">
+      <c r="B193" s="14">
         <f>B187+B188+B189+B192</f>
         <v/>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="15" t="inlineStr">
+      <c r="A194" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B194" s="16">
+      <c r="B194" s="17">
         <f>B193/B187</f>
         <v/>
       </c>
@@ -4738,22 +4749,22 @@
     <row r="195"/>
     <row r="196"/>
     <row r="197">
-      <c r="A197" s="5" t="inlineStr">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>Chermside retail centre</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="12" t="inlineStr">
+      <c r="A198" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="6" t="inlineStr"/>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="A199" s="7" t="inlineStr"/>
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4765,7 +4776,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B200" s="13" t="n">
+      <c r="B200" s="14" t="n">
         <v>4600</v>
       </c>
     </row>
@@ -4775,7 +4786,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B201" s="13" t="n">
+      <c r="B201" s="14" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -4785,7 +4796,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B202" s="13" t="n">
+      <c r="B202" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4795,7 +4806,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B203" s="17" t="n">
+      <c r="B203" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4805,7 +4816,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B204" s="13" t="n">
+      <c r="B204" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4815,7 +4826,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B205" s="13">
+      <c r="B205" s="14">
         <f>-B203*B204</f>
         <v/>
       </c>
@@ -4826,18 +4837,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B206" s="13">
+      <c r="B206" s="14">
         <f>B200+B201+B202+B205</f>
         <v/>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="15" t="inlineStr">
+      <c r="A207" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B207" s="16">
+      <c r="B207" s="17">
         <f>B206/B200</f>
         <v/>
       </c>
@@ -4845,22 +4856,22 @@
     <row r="208"/>
     <row r="209"/>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>Bulimba school</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="12" t="inlineStr">
+      <c r="A211" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr"/>
-      <c r="B212" s="7" t="inlineStr">
+      <c r="A212" s="7" t="inlineStr"/>
+      <c r="B212" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4872,7 +4883,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B213" s="13" t="n">
+      <c r="B213" s="14" t="n">
         <v>3150</v>
       </c>
     </row>
@@ -4882,7 +4893,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B214" s="13" t="n">
+      <c r="B214" s="14" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -4892,7 +4903,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B215" s="13" t="n">
+      <c r="B215" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4902,7 +4913,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B216" s="17" t="n">
+      <c r="B216" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4912,7 +4923,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B217" s="13" t="n">
+      <c r="B217" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4922,7 +4933,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B218" s="13">
+      <c r="B218" s="14">
         <f>-B216*B217</f>
         <v/>
       </c>
@@ -4933,18 +4944,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B219" s="13">
+      <c r="B219" s="14">
         <f>B213+B214+B215+B218</f>
         <v/>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="15" t="inlineStr">
+      <c r="A220" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B220" s="16">
+      <c r="B220" s="17">
         <f>B219/B213</f>
         <v/>
       </c>
@@ -4952,22 +4963,22 @@
     <row r="221"/>
     <row r="222"/>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
+      <c r="A223" s="6" t="inlineStr">
         <is>
           <t>Milton office tower</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="12" t="inlineStr">
+      <c r="A224" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="6" t="inlineStr"/>
-      <c r="B225" s="7" t="inlineStr">
+      <c r="A225" s="7" t="inlineStr"/>
+      <c r="B225" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4979,7 +4990,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B226" s="13" t="n">
+      <c r="B226" s="14" t="n">
         <v>4700</v>
       </c>
     </row>
@@ -4989,7 +5000,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B227" s="13" t="n">
+      <c r="B227" s="14" t="n">
         <v>-90</v>
       </c>
     </row>
@@ -4999,7 +5010,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B228" s="13" t="n">
+      <c r="B228" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5009,7 +5020,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B229" s="17" t="n">
+      <c r="B229" s="18" t="n">
         <v>24</v>
       </c>
     </row>
@@ -5019,7 +5030,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B230" s="13" t="n">
+      <c r="B230" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5029,7 +5040,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B231" s="13">
+      <c r="B231" s="14">
         <f>-B229*B230</f>
         <v/>
       </c>
@@ -5040,18 +5051,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B232" s="13">
+      <c r="B232" s="14">
         <f>B226+B227+B228+B231</f>
         <v/>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="15" t="inlineStr">
+      <c r="A233" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B233" s="16">
+      <c r="B233" s="17">
         <f>B232/B226</f>
         <v/>
       </c>
@@ -5059,22 +5070,22 @@
     <row r="234"/>
     <row r="235"/>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
+      <c r="A236" s="6" t="inlineStr">
         <is>
           <t>West End brewery</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="12" t="inlineStr">
+      <c r="A237" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="6" t="inlineStr"/>
-      <c r="B238" s="7" t="inlineStr">
+      <c r="A238" s="7" t="inlineStr"/>
+      <c r="B238" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5086,7 +5097,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B239" s="13" t="n">
+      <c r="B239" s="14" t="n">
         <v>2900</v>
       </c>
     </row>
@@ -5096,7 +5107,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B240" s="13" t="n">
+      <c r="B240" s="14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5106,7 +5117,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B241" s="13" t="n">
+      <c r="B241" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5116,7 +5127,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B242" s="17" t="n">
+      <c r="B242" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5126,7 +5137,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B243" s="13" t="n">
+      <c r="B243" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5136,7 +5147,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B244" s="13">
+      <c r="B244" s="14">
         <f>-B242*B243</f>
         <v/>
       </c>
@@ -5147,18 +5158,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B245" s="13">
+      <c r="B245" s="14">
         <f>B239+B240+B241+B244</f>
         <v/>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="15" t="inlineStr">
+      <c r="A246" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B246" s="16">
+      <c r="B246" s="17">
         <f>B245/B239</f>
         <v/>
       </c>
@@ -5166,22 +5177,22 @@
     <row r="247"/>
     <row r="248"/>
     <row r="249">
-      <c r="A249" s="5" t="inlineStr">
+      <c r="A249" s="6" t="inlineStr">
         <is>
           <t>Rocklea factory</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="12" t="inlineStr">
+      <c r="A250" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr"/>
-      <c r="B251" s="7" t="inlineStr">
+      <c r="A251" s="7" t="inlineStr"/>
+      <c r="B251" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5193,7 +5204,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B252" s="13" t="n">
+      <c r="B252" s="14" t="n">
         <v>4350</v>
       </c>
     </row>
@@ -5203,7 +5214,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B253" s="13" t="n">
+      <c r="B253" s="14" t="n">
         <v>-110</v>
       </c>
     </row>
@@ -5213,7 +5224,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B254" s="13" t="n">
+      <c r="B254" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5223,7 +5234,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B255" s="17" t="n">
+      <c r="B255" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5233,7 +5244,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B256" s="13" t="n">
+      <c r="B256" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5243,7 +5254,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B257" s="13">
+      <c r="B257" s="14">
         <f>-B255*B256</f>
         <v/>
       </c>
@@ -5254,18 +5265,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B258" s="13">
+      <c r="B258" s="14">
         <f>B252+B253+B254+B257</f>
         <v/>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="15" t="inlineStr">
+      <c r="A259" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B259" s="16">
+      <c r="B259" s="17">
         <f>B258/B252</f>
         <v/>
       </c>
@@ -5273,22 +5284,22 @@
     <row r="260"/>
     <row r="261"/>
     <row r="262">
-      <c r="A262" s="5" t="inlineStr">
+      <c r="A262" s="6" t="inlineStr">
         <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="12" t="inlineStr">
+      <c r="A263" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="inlineStr"/>
-      <c r="B264" s="7" t="inlineStr">
+      <c r="A264" s="7" t="inlineStr"/>
+      <c r="B264" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5300,7 +5311,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B265" s="13" t="n">
+      <c r="B265" s="14" t="n">
         <v>2700</v>
       </c>
     </row>
@@ -5310,7 +5321,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B266" s="13" t="n">
+      <c r="B266" s="14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5320,7 +5331,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B267" s="13" t="n">
+      <c r="B267" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5330,7 +5341,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B268" s="17" t="n">
+      <c r="B268" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5340,7 +5351,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B269" s="13" t="n">
+      <c r="B269" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5350,7 +5361,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B270" s="13">
+      <c r="B270" s="14">
         <f>-B268*B269</f>
         <v/>
       </c>
@@ -5361,18 +5372,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B271" s="13">
+      <c r="B271" s="14">
         <f>B265+B266+B267+B270</f>
         <v/>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="15" t="inlineStr">
+      <c r="A272" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B272" s="16">
+      <c r="B272" s="17">
         <f>B271/B265</f>
         <v/>
       </c>
@@ -5380,27 +5391,27 @@
     <row r="273"/>
     <row r="274"/>
     <row r="275">
-      <c r="A275" s="5" t="inlineStr">
+      <c r="A275" s="6" t="inlineStr">
         <is>
           <t>Trades, Installations: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="12" t="inlineStr">
+      <c r="A276" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr"/>
-      <c r="B277" s="7" t="inlineStr">
+      <c r="A277" s="7" t="inlineStr"/>
+      <c r="B277" s="8" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C277" s="7" t="inlineStr">
+      <c r="C277" s="8" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
@@ -5412,10 +5423,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B278" s="13" t="n">
+      <c r="B278" s="14" t="n">
         <v>79300</v>
       </c>
-      <c r="C278" s="13" t="n">
+      <c r="C278" s="14" t="n">
         <v>84200</v>
       </c>
     </row>
@@ -5425,10 +5436,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B279" s="13" t="n">
+      <c r="B279" s="14" t="n">
         <v>52288</v>
       </c>
-      <c r="C279" s="13" t="n">
+      <c r="C279" s="14" t="n">
         <v>55440</v>
       </c>
     </row>
@@ -5438,26 +5449,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B280" s="13">
+      <c r="B280" s="14">
         <f>B278-B279</f>
         <v/>
       </c>
-      <c r="C280" s="13">
+      <c r="C280" s="14">
         <f>C278-C279</f>
         <v/>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="15" t="inlineStr">
+      <c r="A281" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B281" s="16">
+      <c r="B281" s="17">
         <f>B280/B278</f>
         <v/>
       </c>
-      <c r="C281" s="16">
+      <c r="C281" s="17">
         <f>C280/C278</f>
         <v/>
       </c>
@@ -5465,27 +5476,27 @@
     <row r="282"/>
     <row r="283"/>
     <row r="284">
-      <c r="A284" s="5" t="inlineStr">
+      <c r="A284" s="6" t="inlineStr">
         <is>
           <t>Trades, Installations: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="12" t="inlineStr">
+      <c r="A285" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="6" t="inlineStr"/>
-      <c r="B286" s="7" t="inlineStr">
+      <c r="A286" s="7" t="inlineStr"/>
+      <c r="B286" s="8" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C286" s="7" t="inlineStr">
+      <c r="C286" s="8" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
@@ -5497,10 +5508,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B287" s="13" t="n">
+      <c r="B287" s="14" t="n">
         <v>79300</v>
       </c>
-      <c r="C287" s="13" t="n">
+      <c r="C287" s="14" t="n">
         <v>84200</v>
       </c>
     </row>
@@ -5510,10 +5521,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B288" s="13" t="n">
+      <c r="B288" s="14" t="n">
         <v>52288</v>
       </c>
-      <c r="C288" s="13" t="n">
+      <c r="C288" s="14" t="n">
         <v>55440</v>
       </c>
     </row>
@@ -5523,26 +5534,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B289" s="13">
+      <c r="B289" s="14">
         <f>B287-B288</f>
         <v/>
       </c>
-      <c r="C289" s="13">
+      <c r="C289" s="14">
         <f>C287-C288</f>
         <v/>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="15" t="inlineStr">
+      <c r="A290" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B290" s="16">
+      <c r="B290" s="17">
         <f>B289/B287</f>
         <v/>
       </c>
-      <c r="C290" s="16">
+      <c r="C290" s="17">
         <f>C289/C287</f>
         <v/>
       </c>
@@ -5550,22 +5561,22 @@
     <row r="291"/>
     <row r="292"/>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="12" t="inlineStr">
+      <c r="A294" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr"/>
-      <c r="B295" s="7" t="inlineStr">
+      <c r="A295" s="7" t="inlineStr"/>
+      <c r="B295" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -5577,7 +5588,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B296" s="13" t="n">
+      <c r="B296" s="14" t="n">
         <v>64114</v>
       </c>
     </row>
@@ -5587,7 +5598,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B297" s="13" t="n">
+      <c r="B297" s="14" t="n">
         <v>68218</v>
       </c>
     </row>
@@ -5597,7 +5608,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B298" s="13" t="n">
+      <c r="B298" s="14" t="n">
         <v>37162</v>
       </c>
     </row>
@@ -5607,7 +5618,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B299" s="13">
+      <c r="B299" s="14">
         <f>B297-B298</f>
         <v/>
       </c>
@@ -5618,7 +5629,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B300" s="13">
+      <c r="B300" s="14">
         <f>B296-B299</f>
         <v/>
       </c>
@@ -5629,7 +5640,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B301" s="13" t="n">
+      <c r="B301" s="14" t="n">
         <v>57980</v>
       </c>
     </row>
@@ -5639,7 +5650,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B302" s="13">
+      <c r="B302" s="14">
         <f>B300-B301</f>
         <v/>
       </c>
@@ -5650,7 +5661,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B303" s="13" t="n">
+      <c r="B303" s="14" t="n">
         <v>143566</v>
       </c>
     </row>
@@ -5660,7 +5671,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B304" s="14">
+      <c r="B304" s="15">
         <f>B296/B303</f>
         <v/>
       </c>
@@ -5671,18 +5682,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B305" s="14">
+      <c r="B305" s="15">
         <f>B302/B303</f>
         <v/>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="15" t="inlineStr">
+      <c r="A306" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B306" s="16">
+      <c r="B306" s="17">
         <f>(B299+B301)/B303</f>
         <v/>
       </c>
@@ -5697,22 +5708,22 @@
     <row r="308"/>
     <row r="309"/>
     <row r="310">
-      <c r="A310" s="5" t="inlineStr">
+      <c r="A310" s="6" t="inlineStr">
         <is>
           <t>Aspley cafe data cabling</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="12" t="inlineStr">
+      <c r="A311" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="6" t="inlineStr"/>
-      <c r="B312" s="7" t="inlineStr">
+      <c r="A312" s="7" t="inlineStr"/>
+      <c r="B312" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5724,7 +5735,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B313" s="13" t="n">
+      <c r="B313" s="14" t="n">
         <v>18800</v>
       </c>
     </row>
@@ -5734,7 +5745,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B314" s="13" t="n">
+      <c r="B314" s="14" t="n">
         <v>-4500</v>
       </c>
     </row>
@@ -5744,7 +5755,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B315" s="13" t="n">
+      <c r="B315" s="14" t="n">
         <v>-2000</v>
       </c>
     </row>
@@ -5754,7 +5765,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B316" s="17" t="n">
+      <c r="B316" s="18" t="n">
         <v>58</v>
       </c>
     </row>
@@ -5764,7 +5775,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B317" s="13" t="n">
+      <c r="B317" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5774,7 +5785,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B318" s="13">
+      <c r="B318" s="14">
         <f>-B316*B317</f>
         <v/>
       </c>
@@ -5785,18 +5796,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B319" s="13">
+      <c r="B319" s="14">
         <f>B313+B314+B315+B318</f>
         <v/>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="15" t="inlineStr">
+      <c r="A320" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B320" s="16">
+      <c r="B320" s="17">
         <f>B319/B313</f>
         <v/>
       </c>
@@ -5804,22 +5815,22 @@
     <row r="321"/>
     <row r="322"/>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
         <is>
           <t>Coorparoo shop air-con install</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="12" t="inlineStr">
+      <c r="A324" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr"/>
-      <c r="B325" s="7" t="inlineStr">
+      <c r="A325" s="7" t="inlineStr"/>
+      <c r="B325" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5831,7 +5842,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B326" s="13" t="n">
+      <c r="B326" s="14" t="n">
         <v>20700</v>
       </c>
     </row>
@@ -5841,7 +5852,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B327" s="13" t="n">
+      <c r="B327" s="14" t="n">
         <v>-6900</v>
       </c>
     </row>
@@ -5851,7 +5862,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B328" s="13" t="n">
+      <c r="B328" s="14" t="n">
         <v>-1300</v>
       </c>
     </row>
@@ -5861,7 +5872,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B329" s="17" t="n">
+      <c r="B329" s="18" t="n">
         <v>63</v>
       </c>
     </row>
@@ -5871,7 +5882,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B330" s="13" t="n">
+      <c r="B330" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5881,7 +5892,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B331" s="13">
+      <c r="B331" s="14">
         <f>-B329*B330</f>
         <v/>
       </c>
@@ -5892,18 +5903,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B332" s="13">
+      <c r="B332" s="14">
         <f>B326+B327+B328+B331</f>
         <v/>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="15" t="inlineStr">
+      <c r="A333" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B333" s="16">
+      <c r="B333" s="17">
         <f>B332/B326</f>
         <v/>
       </c>
@@ -5911,22 +5922,22 @@
     <row r="334"/>
     <row r="335"/>
     <row r="336">
-      <c r="A336" s="5" t="inlineStr">
+      <c r="A336" s="6" t="inlineStr">
         <is>
           <t>Salisbury shop solar and battery</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="12" t="inlineStr">
+      <c r="A337" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="6" t="inlineStr"/>
-      <c r="B338" s="7" t="inlineStr">
+      <c r="A338" s="7" t="inlineStr"/>
+      <c r="B338" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5938,7 +5949,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B339" s="13" t="n">
+      <c r="B339" s="14" t="n">
         <v>39800</v>
       </c>
     </row>
@@ -5948,7 +5959,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B340" s="13" t="n">
+      <c r="B340" s="14" t="n">
         <v>-17300</v>
       </c>
     </row>
@@ -5958,7 +5969,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B341" s="13" t="n">
+      <c r="B341" s="14" t="n">
         <v>-3900</v>
       </c>
     </row>
@@ -5968,7 +5979,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B342" s="17" t="n">
+      <c r="B342" s="18" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5978,7 +5989,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B343" s="13" t="n">
+      <c r="B343" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5988,7 +5999,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B344" s="13">
+      <c r="B344" s="14">
         <f>-B342*B343</f>
         <v/>
       </c>
@@ -5999,18 +6010,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B345" s="13">
+      <c r="B345" s="14">
         <f>B339+B340+B341+B344</f>
         <v/>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="15" t="inlineStr">
+      <c r="A346" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B346" s="16">
+      <c r="B346" s="17">
         <f>B345/B339</f>
         <v/>
       </c>
@@ -6018,27 +6029,27 @@
     <row r="347"/>
     <row r="348"/>
     <row r="349">
-      <c r="A349" s="5" t="inlineStr">
+      <c r="A349" s="6" t="inlineStr">
         <is>
           <t>Trades, Call-outs and repairs: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="12" t="inlineStr">
+      <c r="A350" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="6" t="inlineStr"/>
-      <c r="B351" s="7" t="inlineStr">
+      <c r="A351" s="7" t="inlineStr"/>
+      <c r="B351" s="8" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C351" s="7" t="inlineStr">
+      <c r="C351" s="8" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
@@ -6050,10 +6061,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B352" s="13" t="n">
+      <c r="B352" s="14" t="n">
         <v>24166</v>
       </c>
-      <c r="C352" s="13" t="n">
+      <c r="C352" s="14" t="n">
         <v>21677</v>
       </c>
     </row>
@@ -6063,10 +6074,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B353" s="13" t="n">
+      <c r="B353" s="14" t="n">
         <v>12648</v>
       </c>
-      <c r="C353" s="13" t="n">
+      <c r="C353" s="14" t="n">
         <v>11168</v>
       </c>
     </row>
@@ -6076,26 +6087,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B354" s="13">
+      <c r="B354" s="14">
         <f>B352-B353</f>
         <v/>
       </c>
-      <c r="C354" s="13">
+      <c r="C354" s="14">
         <f>C352-C353</f>
         <v/>
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="15" t="inlineStr">
+      <c r="A355" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B355" s="16">
+      <c r="B355" s="17">
         <f>B354/B352</f>
         <v/>
       </c>
-      <c r="C355" s="16">
+      <c r="C355" s="17">
         <f>C354/C352</f>
         <v/>
       </c>
@@ -6103,27 +6114,27 @@
     <row r="356"/>
     <row r="357"/>
     <row r="358">
-      <c r="A358" s="5" t="inlineStr">
+      <c r="A358" s="6" t="inlineStr">
         <is>
           <t>Trades, Call-outs and repairs: gross margin, October and September</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="12" t="inlineStr">
+      <c r="A359" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="6" t="inlineStr"/>
-      <c r="B360" s="7" t="inlineStr">
+      <c r="A360" s="7" t="inlineStr"/>
+      <c r="B360" s="8" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C360" s="7" t="inlineStr">
+      <c r="C360" s="8" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
@@ -6135,10 +6146,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B361" s="13" t="n">
+      <c r="B361" s="14" t="n">
         <v>24166</v>
       </c>
-      <c r="C361" s="13" t="n">
+      <c r="C361" s="14" t="n">
         <v>21677</v>
       </c>
     </row>
@@ -6148,10 +6159,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B362" s="13" t="n">
+      <c r="B362" s="14" t="n">
         <v>12648</v>
       </c>
-      <c r="C362" s="13" t="n">
+      <c r="C362" s="14" t="n">
         <v>11168</v>
       </c>
     </row>
@@ -6161,26 +6172,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B363" s="13">
+      <c r="B363" s="14">
         <f>B361-B362</f>
         <v/>
       </c>
-      <c r="C363" s="13">
+      <c r="C363" s="14">
         <f>C361-C362</f>
         <v/>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="15" t="inlineStr">
+      <c r="A364" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B364" s="16">
+      <c r="B364" s="17">
         <f>B363/B361</f>
         <v/>
       </c>
-      <c r="C364" s="16">
+      <c r="C364" s="17">
         <f>C363/C361</f>
         <v/>
       </c>
@@ -6188,22 +6199,22 @@
     <row r="365"/>
     <row r="366"/>
     <row r="367">
-      <c r="A367" s="5" t="inlineStr">
+      <c r="A367" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, October 2025</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="12" t="inlineStr">
+      <c r="A368" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="6" t="inlineStr"/>
-      <c r="B369" s="7" t="inlineStr">
+      <c r="A369" s="7" t="inlineStr"/>
+      <c r="B369" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -6215,7 +6226,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B370" s="13" t="n">
+      <c r="B370" s="14" t="n">
         <v>64114</v>
       </c>
     </row>
@@ -6225,7 +6236,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B371" s="13" t="n">
+      <c r="B371" s="14" t="n">
         <v>68218</v>
       </c>
     </row>
@@ -6235,7 +6246,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B372" s="13" t="n">
+      <c r="B372" s="14" t="n">
         <v>37162</v>
       </c>
     </row>
@@ -6245,7 +6256,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B373" s="13">
+      <c r="B373" s="14">
         <f>B371-B372</f>
         <v/>
       </c>
@@ -6256,7 +6267,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B374" s="13">
+      <c r="B374" s="14">
         <f>B370-B373</f>
         <v/>
       </c>
@@ -6267,7 +6278,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B375" s="13" t="n">
+      <c r="B375" s="14" t="n">
         <v>57980</v>
       </c>
     </row>
@@ -6277,7 +6288,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B376" s="13">
+      <c r="B376" s="14">
         <f>B374-B375</f>
         <v/>
       </c>
@@ -6288,7 +6299,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B377" s="13" t="n">
+      <c r="B377" s="14" t="n">
         <v>143566</v>
       </c>
     </row>
@@ -6298,7 +6309,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B378" s="14">
+      <c r="B378" s="15">
         <f>B370/B377</f>
         <v/>
       </c>
@@ -6309,18 +6320,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B379" s="14">
+      <c r="B379" s="15">
         <f>B376/B377</f>
         <v/>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="15" t="inlineStr">
+      <c r="A380" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B380" s="16">
+      <c r="B380" s="17">
         <f>(B373+B375)/B377</f>
         <v/>
       </c>
@@ -6335,22 +6346,22 @@
     <row r="382"/>
     <row r="383"/>
     <row r="384">
-      <c r="A384" s="5" t="inlineStr">
+      <c r="A384" s="6" t="inlineStr">
         <is>
           <t>Call-out revenue, October</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="12" t="inlineStr">
+      <c r="A385" s="13" t="inlineStr">
         <is>
           <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="6" t="inlineStr"/>
-      <c r="B386" s="7" t="inlineStr">
+      <c r="A386" s="7" t="inlineStr"/>
+      <c r="B386" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -6362,7 +6373,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B387" s="13" t="n">
+      <c r="B387" s="14" t="n">
         <v>16873</v>
       </c>
     </row>
@@ -6372,7 +6383,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B388" s="13" t="n">
+      <c r="B388" s="14" t="n">
         <v>5610</v>
       </c>
     </row>
@@ -6382,7 +6393,7 @@
           <t>Mark-up on materials</t>
         </is>
       </c>
-      <c r="B389" s="14" t="n">
+      <c r="B389" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -6392,7 +6403,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B390" s="13">
+      <c r="B390" s="14">
         <f>B388*(1+B389)</f>
         <v/>
       </c>
@@ -6403,7 +6414,7 @@
           <t>Materials charged (as invoiced, rounded per call-out)</t>
         </is>
       </c>
-      <c r="B391" s="13" t="n">
+      <c r="B391" s="14" t="n">
         <v>7293</v>
       </c>
     </row>
@@ -6413,18 +6424,18 @@
           <t>Call-out revenue</t>
         </is>
       </c>
-      <c r="B392" s="13">
+      <c r="B392" s="14">
         <f>B387+B391</f>
         <v/>
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="15" t="inlineStr">
+      <c r="A393" s="16" t="inlineStr">
         <is>
           <t>Technician time, % of call-out revenue</t>
         </is>
       </c>
-      <c r="B393" s="16">
+      <c r="B393" s="17">
         <f>B387/B392</f>
         <v/>
       </c>
@@ -6432,22 +6443,22 @@
     <row r="394"/>
     <row r="395"/>
     <row r="396">
-      <c r="A396" s="5" t="inlineStr">
+      <c r="A396" s="6" t="inlineStr">
         <is>
           <t>Call-out revenue, October</t>
         </is>
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="12" t="inlineStr">
+      <c r="A397" s="13" t="inlineStr">
         <is>
           <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="6" t="inlineStr"/>
-      <c r="B398" s="7" t="inlineStr">
+      <c r="A398" s="7" t="inlineStr"/>
+      <c r="B398" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -6459,7 +6470,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B399" s="13" t="n">
+      <c r="B399" s="14" t="n">
         <v>16873</v>
       </c>
     </row>
@@ -6469,7 +6480,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B400" s="13" t="n">
+      <c r="B400" s="14" t="n">
         <v>5610</v>
       </c>
     </row>
@@ -6479,7 +6490,7 @@
           <t>Mark-up on materials</t>
         </is>
       </c>
-      <c r="B401" s="14" t="n">
+      <c r="B401" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -6489,7 +6500,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B402" s="13">
+      <c r="B402" s="14">
         <f>B400*(1+B401)</f>
         <v/>
       </c>
@@ -6500,7 +6511,7 @@
           <t>Materials charged (as invoiced, rounded per call-out)</t>
         </is>
       </c>
-      <c r="B403" s="13" t="n">
+      <c r="B403" s="14" t="n">
         <v>7293</v>
       </c>
     </row>
@@ -6510,18 +6521,18 @@
           <t>Call-out revenue</t>
         </is>
       </c>
-      <c r="B404" s="13">
+      <c r="B404" s="14">
         <f>B399+B403</f>
         <v/>
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="15" t="inlineStr">
+      <c r="A405" s="16" t="inlineStr">
         <is>
           <t>Technician time, % of call-out revenue</t>
         </is>
       </c>
-      <c r="B405" s="16">
+      <c r="B405" s="17">
         <f>B399/B404</f>
         <v/>
       </c>
@@ -6529,22 +6540,22 @@
     <row r="406"/>
     <row r="407"/>
     <row r="408">
-      <c r="A408" s="5" t="inlineStr">
+      <c r="A408" s="6" t="inlineStr">
         <is>
           <t>1-hour call-outs (7)</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="12" t="inlineStr">
+      <c r="A409" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in October, added together</t>
         </is>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="6" t="inlineStr"/>
-      <c r="B410" s="7" t="inlineStr">
+      <c r="A410" s="7" t="inlineStr"/>
+      <c r="B410" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -6556,7 +6567,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B411" s="13" t="n">
+      <c r="B411" s="14" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6566,7 +6577,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B412" s="13" t="n">
+      <c r="B412" s="14" t="n">
         <v>1141</v>
       </c>
     </row>
@@ -6576,7 +6587,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B413" s="13" t="n">
+      <c r="B413" s="14" t="n">
         <v>1053</v>
       </c>
     </row>
@@ -6586,7 +6597,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B414" s="13">
+      <c r="B414" s="14">
         <f>B412+B413</f>
         <v/>
       </c>
@@ -6597,7 +6608,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B415" s="13" t="n">
+      <c r="B415" s="14" t="n">
         <v>-810</v>
       </c>
     </row>
@@ -6607,7 +6618,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B416" s="13" t="n">
+      <c r="B416" s="14" t="n">
         <v>-476</v>
       </c>
     </row>
@@ -6617,18 +6628,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B417" s="13">
+      <c r="B417" s="14">
         <f>B414+B415+B416</f>
         <v/>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="15" t="inlineStr">
+      <c r="A418" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B418" s="16">
+      <c r="B418" s="17">
         <f>B417/B414</f>
         <v/>
       </c>
@@ -6636,22 +6647,22 @@
     <row r="419"/>
     <row r="420"/>
     <row r="421">
-      <c r="A421" s="5" t="inlineStr">
+      <c r="A421" s="6" t="inlineStr">
         <is>
           <t>1.5-hour call-outs (3)</t>
         </is>
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="12" t="inlineStr">
+      <c r="A422" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in October, added together</t>
         </is>
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="6" t="inlineStr"/>
-      <c r="B423" s="7" t="inlineStr">
+      <c r="A423" s="7" t="inlineStr"/>
+      <c r="B423" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -6663,7 +6674,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B424" s="13" t="n">
+      <c r="B424" s="14" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6673,7 +6684,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B425" s="13" t="n">
+      <c r="B425" s="14" t="n">
         <v>735</v>
       </c>
     </row>
@@ -6683,7 +6694,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B426" s="13" t="n">
+      <c r="B426" s="14" t="n">
         <v>637</v>
       </c>
     </row>
@@ -6693,7 +6704,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B427" s="13">
+      <c r="B427" s="14">
         <f>B425+B426</f>
         <v/>
       </c>
@@ -6704,7 +6715,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B428" s="13" t="n">
+      <c r="B428" s="14" t="n">
         <v>-490</v>
       </c>
     </row>
@@ -6714,7 +6725,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B429" s="13" t="n">
+      <c r="B429" s="14" t="n">
         <v>-306</v>
       </c>
     </row>
@@ -6724,18 +6735,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B430" s="13">
+      <c r="B430" s="14">
         <f>B427+B428+B429</f>
         <v/>
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="15" t="inlineStr">
+      <c r="A431" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B431" s="16">
+      <c r="B431" s="17">
         <f>B430/B427</f>
         <v/>
       </c>
@@ -6743,22 +6754,22 @@
     <row r="432"/>
     <row r="433"/>
     <row r="434">
-      <c r="A434" s="5" t="inlineStr">
+      <c r="A434" s="6" t="inlineStr">
         <is>
           <t>2-hour call-outs (9)</t>
         </is>
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="12" t="inlineStr">
+      <c r="A435" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in October, added together</t>
         </is>
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="6" t="inlineStr"/>
-      <c r="B436" s="7" t="inlineStr">
+      <c r="A436" s="7" t="inlineStr"/>
+      <c r="B436" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -6770,7 +6781,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B437" s="13" t="n">
+      <c r="B437" s="14" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6780,7 +6791,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B438" s="13" t="n">
+      <c r="B438" s="14" t="n">
         <v>2934</v>
       </c>
     </row>
@@ -6790,7 +6801,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B439" s="13" t="n">
+      <c r="B439" s="14" t="n">
         <v>1833</v>
       </c>
     </row>
@@ -6800,7 +6811,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B440" s="13">
+      <c r="B440" s="14">
         <f>B438+B439</f>
         <v/>
       </c>
@@ -6811,7 +6822,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B441" s="13" t="n">
+      <c r="B441" s="14" t="n">
         <v>-1410</v>
       </c>
     </row>
@@ -6821,7 +6832,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B442" s="13" t="n">
+      <c r="B442" s="14" t="n">
         <v>-1224</v>
       </c>
     </row>
@@ -6831,18 +6842,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B443" s="13">
+      <c r="B443" s="14">
         <f>B440+B441+B442</f>
         <v/>
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="15" t="inlineStr">
+      <c r="A444" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B444" s="16">
+      <c r="B444" s="17">
         <f>B443/B440</f>
         <v/>
       </c>
@@ -6850,22 +6861,22 @@
     <row r="445"/>
     <row r="446"/>
     <row r="447">
-      <c r="A447" s="5" t="inlineStr">
+      <c r="A447" s="6" t="inlineStr">
         <is>
           <t>2.5-hour call-outs (8)</t>
         </is>
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="12" t="inlineStr">
+      <c r="A448" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in October, added together</t>
         </is>
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="6" t="inlineStr"/>
-      <c r="B449" s="7" t="inlineStr">
+      <c r="A449" s="7" t="inlineStr"/>
+      <c r="B449" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -6877,7 +6888,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B450" s="13" t="n">
+      <c r="B450" s="14" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6887,7 +6898,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B451" s="13" t="n">
+      <c r="B451" s="14" t="n">
         <v>3261</v>
       </c>
     </row>
@@ -6897,7 +6908,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B452" s="13" t="n">
+      <c r="B452" s="14" t="n">
         <v>1235</v>
       </c>
     </row>
@@ -6907,7 +6918,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B453" s="13">
+      <c r="B453" s="14">
         <f>B451+B452</f>
         <v/>
       </c>
@@ -6918,7 +6929,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B454" s="13" t="n">
+      <c r="B454" s="14" t="n">
         <v>-950</v>
       </c>
     </row>
@@ -6928,7 +6939,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B455" s="13" t="n">
+      <c r="B455" s="14" t="n">
         <v>-1360</v>
       </c>
     </row>
@@ -6938,18 +6949,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B456" s="13">
+      <c r="B456" s="14">
         <f>B453+B454+B455</f>
         <v/>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="15" t="inlineStr">
+      <c r="A457" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B457" s="16">
+      <c r="B457" s="17">
         <f>B456/B453</f>
         <v/>
       </c>
@@ -6957,22 +6968,22 @@
     <row r="458"/>
     <row r="459"/>
     <row r="460">
-      <c r="A460" s="5" t="inlineStr">
+      <c r="A460" s="6" t="inlineStr">
         <is>
           <t>3-hour call-outs (10)</t>
         </is>
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="12" t="inlineStr">
+      <c r="A461" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in October, added together</t>
         </is>
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="6" t="inlineStr"/>
-      <c r="B462" s="7" t="inlineStr">
+      <c r="A462" s="7" t="inlineStr"/>
+      <c r="B462" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -6984,7 +6995,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B463" s="13" t="n">
+      <c r="B463" s="14" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6994,7 +7005,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B464" s="13" t="n">
+      <c r="B464" s="14" t="n">
         <v>4890</v>
       </c>
     </row>
@@ -7004,7 +7015,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B465" s="13" t="n">
+      <c r="B465" s="14" t="n">
         <v>1430</v>
       </c>
     </row>
@@ -7014,7 +7025,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B466" s="13">
+      <c r="B466" s="14">
         <f>B464+B465</f>
         <v/>
       </c>
@@ -7025,7 +7036,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B467" s="13" t="n">
+      <c r="B467" s="14" t="n">
         <v>-1100</v>
       </c>
     </row>
@@ -7035,7 +7046,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B468" s="13" t="n">
+      <c r="B468" s="14" t="n">
         <v>-2040</v>
       </c>
     </row>
@@ -7045,18 +7056,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B469" s="13">
+      <c r="B469" s="14">
         <f>B466+B467+B468</f>
         <v/>
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="15" t="inlineStr">
+      <c r="A470" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B470" s="16">
+      <c r="B470" s="17">
         <f>B469/B466</f>
         <v/>
       </c>
@@ -7064,22 +7075,22 @@
     <row r="471"/>
     <row r="472"/>
     <row r="473">
-      <c r="A473" s="5" t="inlineStr">
+      <c r="A473" s="6" t="inlineStr">
         <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="12" t="inlineStr">
+      <c r="A474" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in October, added together</t>
         </is>
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="6" t="inlineStr"/>
-      <c r="B475" s="7" t="inlineStr">
+      <c r="A475" s="7" t="inlineStr"/>
+      <c r="B475" s="8" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
@@ -7091,7 +7102,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B476" s="13" t="n">
+      <c r="B476" s="14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7101,7 +7112,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B477" s="13" t="n">
+      <c r="B477" s="14" t="n">
         <v>3912</v>
       </c>
     </row>
@@ -7111,7 +7122,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B478" s="13" t="n">
+      <c r="B478" s="14" t="n">
         <v>1105</v>
       </c>
     </row>
@@ -7121,7 +7132,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B479" s="13">
+      <c r="B479" s="14">
         <f>B477+B478</f>
         <v/>
       </c>
@@ -7132,7 +7143,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B480" s="13" t="n">
+      <c r="B480" s="14" t="n">
         <v>-850</v>
       </c>
     </row>
@@ -7142,7 +7153,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B481" s="13" t="n">
+      <c r="B481" s="14" t="n">
         <v>-1632</v>
       </c>
     </row>
@@ -7152,18 +7163,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B482" s="13">
+      <c r="B482" s="14">
         <f>B479+B480+B481</f>
         <v/>
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="15" t="inlineStr">
+      <c r="A483" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B483" s="16">
+      <c r="B483" s="17">
         <f>B482/B479</f>
         <v/>
       </c>
@@ -7177,7 +7188,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7454,1656 +7465,1656 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2025 · Data status: Sep 2025 locked · Oct 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>191014</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>114334</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="15">
         <f>IF(D6=0,"",F6/D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>200124</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>113016</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="15">
         <f>IF(D7=0,"",F7/D7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>159406</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>85316</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <f>IF(D8=0,"",F8/D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>156794</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>80742</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="15">
         <f>IF(D9=0,"",F9/D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>179190</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>102348</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="15">
         <f>IF(D10=0,"",F10/D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>150465</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>85752</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="15">
         <f>IF(D11=0,"",F11/D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>138865</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <v>76808</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="15">
         <f>IF(D12=0,"",F12/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>144649</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <v>83700</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="15">
         <f>IF(D13=0,"",F13/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>183265</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <v>97584</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="15">
         <f>IF(D14=0,"",F14/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>208588</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <v>120326</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="15">
         <f>IF(D15=0,"",F15/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>155118</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>78258</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f>D16-E16</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="15">
         <f>IF(D16=0,"",F16/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>143077</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="14" t="n">
         <v>80054</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>D17-E17</f>
         <v/>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="15">
         <f>IF(D17=0,"",F17/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>143566</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <v>79452</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <f>D18-E18</f>
         <v/>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="15">
         <f>IF(D18=0,"",F18/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <f>D19-E19</f>
         <v/>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="15">
         <f>IF(D19=0,"",F19/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <f>D20-E20</f>
         <v/>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="15">
         <f>IF(D20=0,"",F20/D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <f>D21-E21</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="15">
         <f>IF(D21=0,"",F21/D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <f>D22-E22</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="15">
         <f>IF(D22=0,"",F22/D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="14">
         <f>D23-E23</f>
         <v/>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="15">
         <f>IF(D23=0,"",F23/D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="14">
         <f>D24-E24</f>
         <v/>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="15">
         <f>IF(D24=0,"",F24/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <f>D25-E25</f>
         <v/>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="15">
         <f>IF(D25=0,"",F25/D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <f>D26-E26</f>
         <v/>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="15">
         <f>IF(D26=0,"",F26/D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="14" t="n">
         <v>35720</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="14">
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="15">
         <f>IF(D27=0,"",F27/D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="14">
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="15">
         <f>IF(D28=0,"",F28/D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="14">
         <f>D29-E29</f>
         <v/>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="15">
         <f>IF(D29=0,"",F29/D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="14">
         <f>D30-E30</f>
         <v/>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="15">
         <f>IF(D30=0,"",F30/D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <f>D31-E31</f>
         <v/>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="15">
         <f>IF(D31=0,"",F31/D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="14" t="n">
         <v>141600</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="14" t="n">
         <v>92430</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="14">
         <f>D32-E32</f>
         <v/>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="15">
         <f>IF(D32=0,"",F32/D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="14" t="n">
         <v>147100</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="14" t="n">
         <v>89070</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="14">
         <f>D33-E33</f>
         <v/>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="15">
         <f>IF(D33=0,"",F33/D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="14" t="n">
         <v>103700</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="14" t="n">
         <v>59908</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="14">
         <f>D34-E34</f>
         <v/>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="15">
         <f>IF(D34=0,"",F34/D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="14" t="n">
         <v>100100</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="14" t="n">
         <v>54678</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="14">
         <f>D35-E35</f>
         <v/>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="15">
         <f>IF(D35=0,"",F35/D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="14" t="n">
         <v>118600</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="14" t="n">
         <v>74966</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="14">
         <f>D36-E36</f>
         <v/>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="15">
         <f>IF(D36=0,"",F36/D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="14" t="n">
         <v>96400</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="14" t="n">
         <v>61664</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="14">
         <f>D37-E37</f>
         <v/>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="15">
         <f>IF(D37=0,"",F37/D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="14" t="n">
         <v>83900</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="14" t="n">
         <v>52264</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="14">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="15">
         <f>IF(D38=0,"",F38/D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="14" t="n">
         <v>89900</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="14" t="n">
         <v>59534</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="14">
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="15">
         <f>IF(D39=0,"",F39/D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="14" t="n">
         <v>126300</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="14" t="n">
         <v>72976</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="14">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="15">
         <f>IF(D40=0,"",F40/D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="14" t="n">
         <v>152100</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="14" t="n">
         <v>96920</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="14">
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="15">
         <f>IF(D41=0,"",F41/D41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="14" t="n">
         <v>96500</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E42" s="14" t="n">
         <v>53590</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="14">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="15">
         <f>IF(D42=0,"",F42/D42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="14" t="n">
         <v>84200</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="14" t="n">
         <v>55440</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="14">
         <f>D43-E43</f>
         <v/>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="15">
         <f>IF(D43=0,"",F43/D43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="14" t="n">
         <v>79300</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E44" s="14" t="n">
         <v>52288</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="14">
         <f>D44-E44</f>
         <v/>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="15">
         <f>IF(D44=0,"",F44/D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="14" t="n">
         <v>21764</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="14" t="n">
         <v>11484</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="14">
         <f>D45-E45</f>
         <v/>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="15">
         <f>IF(D45=0,"",F45/D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="14" t="n">
         <v>25374</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" s="14" t="n">
         <v>13526</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="14">
         <f>D46-E46</f>
         <v/>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="15">
         <f>IF(D46=0,"",F46/D46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="14" t="n">
         <v>28056</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="14" t="n">
         <v>14988</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="14">
         <f>D47-E47</f>
         <v/>
       </c>
-      <c r="G47" s="14">
+      <c r="G47" s="15">
         <f>IF(D47=0,"",F47/D47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="14" t="n">
         <v>29044</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="14" t="n">
         <v>15644</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="14">
         <f>D48-E48</f>
         <v/>
       </c>
-      <c r="G48" s="14">
+      <c r="G48" s="15">
         <f>IF(D48=0,"",F48/D48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="14" t="n">
         <v>29290</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E49" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="14">
         <f>D49-E49</f>
         <v/>
       </c>
-      <c r="G49" s="14">
+      <c r="G49" s="15">
         <f>IF(D49=0,"",F49/D49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="14" t="n">
         <v>22765</v>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" s="14" t="n">
         <v>12306</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50" s="14">
         <f>D50-E50</f>
         <v/>
       </c>
-      <c r="G50" s="14">
+      <c r="G50" s="15">
         <f>IF(D50=0,"",F50/D50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="14" t="n">
         <v>23665</v>
       </c>
-      <c r="E51" s="13" t="n">
+      <c r="E51" s="14" t="n">
         <v>12762</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="14">
         <f>D51-E51</f>
         <v/>
       </c>
-      <c r="G51" s="14">
+      <c r="G51" s="15">
         <f>IF(D51=0,"",F51/D51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="14" t="n">
         <v>23449</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="14" t="n">
         <v>12384</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F52" s="14">
         <f>D52-E52</f>
         <v/>
       </c>
-      <c r="G52" s="14">
+      <c r="G52" s="15">
         <f>IF(D52=0,"",F52/D52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="14" t="n">
         <v>21245</v>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E53" s="14" t="n">
         <v>11162</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="14">
         <f>D53-E53</f>
         <v/>
       </c>
-      <c r="G53" s="14">
+      <c r="G53" s="15">
         <f>IF(D53=0,"",F53/D53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="14" t="n">
         <v>19288</v>
       </c>
-      <c r="E54" s="13" t="n">
+      <c r="E54" s="14" t="n">
         <v>9960</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="14">
         <f>D54-E54</f>
         <v/>
       </c>
-      <c r="G54" s="14">
+      <c r="G54" s="15">
         <f>IF(D54=0,"",F54/D54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="14" t="n">
         <v>21418</v>
       </c>
-      <c r="E55" s="13" t="n">
+      <c r="E55" s="14" t="n">
         <v>11222</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="14">
         <f>D55-E55</f>
         <v/>
       </c>
-      <c r="G55" s="14">
+      <c r="G55" s="15">
         <f>IF(D55=0,"",F55/D55)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="14" t="n">
         <v>21677</v>
       </c>
-      <c r="E56" s="13" t="n">
+      <c r="E56" s="14" t="n">
         <v>11168</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="14">
         <f>D56-E56</f>
         <v/>
       </c>
-      <c r="G56" s="14">
+      <c r="G56" s="15">
         <f>IF(D56=0,"",F56/D56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="14" t="n">
         <v>24166</v>
       </c>
-      <c r="E57" s="13" t="n">
+      <c r="E57" s="14" t="n">
         <v>12648</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="14">
         <f>D57-E57</f>
         <v/>
       </c>
-      <c r="G57" s="14">
+      <c r="G57" s="15">
         <f>IF(D57=0,"",F57/D57)</f>
         <v/>
       </c>
@@ -9114,7 +9125,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
